--- a/examples/wangetal2018/out/ResultFiles/AC_1.0_b.xlsx
+++ b/examples/wangetal2018/out/ResultFiles/AC_1.0_b.xlsx
@@ -14,17 +14,18 @@
     <sheet name="Compressor design" sheetId="5" r:id="rId5"/>
     <sheet name="Pressure profile" sheetId="6" r:id="rId6"/>
     <sheet name="Demand error" sheetId="7" r:id="rId7"/>
+    <sheet name="ProFAST" sheetId="8" r:id="rId8"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="418" uniqueCount="212">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="670" uniqueCount="328">
   <si>
     <t xml:space="preserve">
 ---------DISCLAIMER---------
-AS NOTED IN THE LICENSE, ALLIANCE FOR SUSTAINABLE ENERGY, LLC: (i) DISCLAIMS ANY WARRANTIES, EXPRESS OR IMPLIED, INCLUDING BUT NOT LIMITED TO ANY IMPLIED WARRANTIES OF MERCHANTABILITY, FITNESS FOR A PARTICULAR PURPOSE, TITLE OR NON-INFRINGEMENT, AND (ii) DOES NOT ASSUME ANY LEGAL LIABILITY OR RESPONSIBILITY FOR THE ACCURACY, COMPLETENESS, OR USEFULNESS OF SOFTWARE OR ITS OUTPUTS. ANY RELIANCE BY THE USER ON THE SOFTWARE IS DONE AT THE USER’S OWN RISK.
+AS NOTED IN THE LICENSE, ALLIANCE FOR ENERGY INNOVATION, LLC: (i) DISCLAIMS ANY WARRANTIES, EXPRESS OR IMPLIED, INCLUDING BUT NOT LIMITED TO ANY IMPLIED WARRANTIES OF MERCHANTABILITY, FITNESS FOR A PARTICULAR PURPOSE, TITLE OR NON-INFRINGEMENT, AND (ii) DOES NOT ASSUME ANY LEGAL LIABILITY OR RESPONSIBILITY FOR THE ACCURACY, COMPLETENESS, OR USEFULNESS OF SOFTWARE OR ITS OUTPUTS. ANY RELIANCE BY THE USER ON THE SOFTWARE IS DONE AT THE USER’S OWN RISK.
 BlendPATH was developed to provide the user with economic analytical capabilities to evaluate potential natural gas transmission pipeline modifications for accommodating hydrogen blending or pure hydrogen streams and to assess the potential associated economic impacts. This model is intended for use during the early stages of pipeline repurposing concept evaluation, which is defined here as the initial project phase when the developer has already gathered the relevant pipeline material design and operation data but has not yet conducted the detailed pipeline materials testing, as specified in ASME B31.12, or performed the in-line inspections that qualify a given pipeline section for hydrogen or hydrogen blending service. Despite BlendPATH using ASME B31.12 to assess existing natural gas transmission pipelines and establish potential pipeline modifications for a natural gas transmission pipeline network to meet ASME B31.12 design requirements, BlendPATH does not qualify the examined pipeline network or modifications thereof for pure hydrogen or hydrogen blending. Pipeline owners and operators must conduct additional evaluations as specified in ASME B31.12 and other relevant code and regulations, independent of BlendPATH application, to qualify actual natural gas transmission pipelines for operation with hydrogen. Failure to do so may result in pipeline fatigue and/or rupture. It is the sole responsibility of the pipeline owner and operator to ensure that their pipeline qualifies for the ASME B31.12 design option that they choose, and any other relevant code and regulations, and that any defects present in the pipeline are acceptable at the operating pressure chosen.
 ----------------------------
 </t>
@@ -39,12 +40,21 @@
     <t>Network name</t>
   </si>
   <si>
+    <t>examples/wangetal2018</t>
+  </si>
+  <si>
     <t>Save directory</t>
   </si>
   <si>
+    <t>out</t>
+  </si>
+  <si>
     <t>Design option - original</t>
   </si>
   <si>
+    <t>b</t>
+  </si>
+  <si>
     <t>Location class</t>
   </si>
   <si>
@@ -57,6 +67,9 @@
     <t>Compression ratio</t>
   </si>
   <si>
+    <t>[1.2, 1.4, 1.6, 1.8, 2.0]</t>
+  </si>
+  <si>
     <t>Blending ratio</t>
   </si>
   <si>
@@ -75,18 +88,24 @@
     <t>Region</t>
   </si>
   <si>
+    <t>GP</t>
+  </si>
+  <si>
     <t>Modification method</t>
   </si>
   <si>
+    <t>ac</t>
+  </si>
+  <si>
     <t>Modification design option</t>
   </si>
   <si>
-    <t>Verbose</t>
-  </si>
-  <si>
     <t>Equation of state</t>
   </si>
   <si>
+    <t>rk</t>
+  </si>
+  <si>
     <t>Inline inspection inspection interval</t>
   </si>
   <si>
@@ -111,25 +130,40 @@
     <t>New electric compressor driver efficiency</t>
   </si>
   <si>
-    <t>examples/wangetal2018</t>
-  </si>
-  <si>
-    <t>out</t>
-  </si>
-  <si>
-    <t>b</t>
-  </si>
-  <si>
-    <t>[1.2, 1.4, 1.6, 1.8, 2.0]</t>
-  </si>
-  <si>
-    <t>GP</t>
-  </si>
-  <si>
-    <t>ac</t>
-  </si>
-  <si>
-    <t>rk</t>
+    <t>Pipe price markup</t>
+  </si>
+  <si>
+    <t>Compressor price markup</t>
+  </si>
+  <si>
+    <t>Financial overrides</t>
+  </si>
+  <si>
+    <t>{}</t>
+  </si>
+  <si>
+    <t>Filename suffix</t>
+  </si>
+  <si>
+    <t>Thermodynamic curvefits enabled</t>
+  </si>
+  <si>
+    <t>Composition tracking enabled</t>
+  </si>
+  <si>
+    <t>Scenario type</t>
+  </si>
+  <si>
+    <t>transmission</t>
+  </si>
+  <si>
+    <t>Polymer cost type</t>
+  </si>
+  <si>
+    <t>socal</t>
+  </si>
+  <si>
+    <t>Max velocity allowed in distribution networks</t>
   </si>
   <si>
     <t>Parameter</t>
@@ -141,6 +175,9 @@
     <t>LCOT: Levelized cost of transport</t>
   </si>
   <si>
+    <t>$/MMBTU</t>
+  </si>
+  <si>
     <t>LCOT: New pipe CapEx</t>
   </si>
   <si>
@@ -177,6 +214,12 @@
     <t>LCOT: Supply commpressor fuel</t>
   </si>
   <si>
+    <t>LCOT: Meter set assembly</t>
+  </si>
+  <si>
+    <t>LCOT: Gas pressure regulation and metering station</t>
+  </si>
+  <si>
     <t>LCOT: Fixed O&amp;M</t>
   </si>
   <si>
@@ -189,6 +232,9 @@
     <t>Hydrogen injection price</t>
   </si>
   <si>
+    <t>$/kg</t>
+  </si>
+  <si>
     <t>Natural gas price</t>
   </si>
   <si>
@@ -198,27 +244,48 @@
     <t>Pipeline capacity (daily)</t>
   </si>
   <si>
+    <t>MMBTU/day</t>
+  </si>
+  <si>
     <t>Pipeline capacity (hour)</t>
   </si>
   <si>
+    <t>MMBTU/hr</t>
+  </si>
+  <si>
     <t>Added pipeline</t>
   </si>
   <si>
+    <t>km</t>
+  </si>
+  <si>
+    <t>mi</t>
+  </si>
+  <si>
     <t>Added compressor stations</t>
   </si>
   <si>
     <t>Added compressor capacity</t>
   </si>
   <si>
+    <t>hp</t>
+  </si>
+  <si>
     <t>Compressor fuel usage</t>
   </si>
   <si>
     <t>Compressor fuel usage (electric)</t>
   </si>
   <si>
+    <t>kW</t>
+  </si>
+  <si>
     <t>New pipe</t>
   </si>
   <si>
+    <t>$</t>
+  </si>
+  <si>
     <t>New compressor stations</t>
   </si>
   <si>
@@ -231,39 +298,30 @@
     <t>Valve modifications</t>
   </si>
   <si>
+    <t>Meter set assembly</t>
+  </si>
+  <si>
+    <t>Gas pressure regulating metering station</t>
+  </si>
+  <si>
     <t>Hydrogen energy ratio</t>
   </si>
   <si>
-    <t>$/MMBTU</t>
-  </si>
-  <si>
-    <t>$/kg</t>
-  </si>
-  <si>
-    <t>MMBTU/day</t>
-  </si>
-  <si>
-    <t>MMBTU/hr</t>
-  </si>
-  <si>
-    <t>km</t>
-  </si>
-  <si>
-    <t>mi</t>
-  </si>
-  <si>
-    <t>hp</t>
-  </si>
-  <si>
-    <t>kW</t>
-  </si>
-  <si>
-    <t>$</t>
-  </si>
-  <si>
     <t>%</t>
   </si>
   <si>
+    <t>Emissions intensity (total)</t>
+  </si>
+  <si>
+    <t>kgCO2e/MMBTU</t>
+  </si>
+  <si>
+    <t>Total emissions (annual)</t>
+  </si>
+  <si>
+    <t>MMTCO2e/yr</t>
+  </si>
+  <si>
     <t>Breakdown of original pipe by diameter, schedule and grade</t>
   </si>
   <si>
@@ -279,6 +337,9 @@
     <t>Schedule</t>
   </si>
   <si>
+    <t>Polymer</t>
+  </si>
+  <si>
     <t>X60</t>
   </si>
   <si>
@@ -339,9 +400,6 @@
     <t>C_1_0</t>
   </si>
   <si>
-    <t>C_1_1</t>
-  </si>
-  <si>
     <t>CS2</t>
   </si>
   <si>
@@ -402,198 +460,189 @@
     <t>PI01_0</t>
   </si>
   <si>
+    <t>N01</t>
+  </si>
+  <si>
+    <t>N01_0</t>
+  </si>
+  <si>
+    <t>Existing</t>
+  </si>
+  <si>
     <t>PI01_1</t>
   </si>
   <si>
+    <t>N01_1</t>
+  </si>
+  <si>
     <t>PI01_pre_C_0_0</t>
   </si>
   <si>
+    <t>N_pre_C_0_0</t>
+  </si>
+  <si>
     <t>PI01_remaining</t>
   </si>
   <si>
+    <t>N_post_C_0_0</t>
+  </si>
+  <si>
+    <t>N02</t>
+  </si>
+  <si>
     <t>PI02_0</t>
   </si>
   <si>
+    <t>N02_0</t>
+  </si>
+  <si>
     <t>PI02</t>
   </si>
   <si>
+    <t>N03</t>
+  </si>
+  <si>
     <t>PI03_0</t>
   </si>
   <si>
+    <t>N03_C</t>
+  </si>
+  <si>
+    <t>N03_C_0</t>
+  </si>
+  <si>
     <t>PI03</t>
   </si>
   <si>
-    <t>PI04_0_pre_C_1_0</t>
-  </si>
-  <si>
-    <t>PI04_0_remaining</t>
+    <t>N04</t>
+  </si>
+  <si>
+    <t>PI04_0</t>
+  </si>
+  <si>
+    <t>N04_0</t>
   </si>
   <si>
     <t>PI04_1</t>
   </si>
   <si>
-    <t>PI04</t>
-  </si>
-  <si>
-    <t>PI05_0_pre_C_1_1</t>
-  </si>
-  <si>
-    <t>PI05_0_remaining</t>
+    <t>N04_1</t>
+  </si>
+  <si>
+    <t>PI04_pre_C_1_0</t>
+  </si>
+  <si>
+    <t>N_pre_C_1_0</t>
+  </si>
+  <si>
+    <t>PI04_remaining</t>
+  </si>
+  <si>
+    <t>N_post_C_1_0</t>
+  </si>
+  <si>
+    <t>N05</t>
+  </si>
+  <si>
+    <t>PI05_0</t>
+  </si>
+  <si>
+    <t>N05_0</t>
   </si>
   <si>
     <t>PI05_1</t>
   </si>
   <si>
+    <t>N05_1</t>
+  </si>
+  <si>
     <t>PI05</t>
   </si>
   <si>
+    <t>N06</t>
+  </si>
+  <si>
     <t>PI06_0</t>
   </si>
   <si>
+    <t>N06_C</t>
+  </si>
+  <si>
+    <t>N06_C_0</t>
+  </si>
+  <si>
     <t>PI06_1</t>
   </si>
   <si>
+    <t>N06_C_1</t>
+  </si>
+  <si>
     <t>PI06</t>
   </si>
   <si>
+    <t>N_pre_C_2_0</t>
+  </si>
+  <si>
     <t>PI07_0_remaining</t>
   </si>
   <si>
+    <t>N07</t>
+  </si>
+  <si>
+    <t>N07_0</t>
+  </si>
+  <si>
     <t>PI07_1</t>
   </si>
   <si>
+    <t>N07_1</t>
+  </si>
+  <si>
     <t>PI07</t>
   </si>
   <si>
+    <t>N08</t>
+  </si>
+  <si>
     <t>PI08_0</t>
   </si>
   <si>
+    <t>N08_C</t>
+  </si>
+  <si>
+    <t>N08_C_0</t>
+  </si>
+  <si>
     <t>PI08_1</t>
   </si>
   <si>
+    <t>N08_C_1</t>
+  </si>
+  <si>
     <t>PI08</t>
   </si>
   <si>
+    <t>N09</t>
+  </si>
+  <si>
     <t>PI09_0</t>
   </si>
   <si>
+    <t>N09_0</t>
+  </si>
+  <si>
     <t>PI09_1</t>
   </si>
   <si>
+    <t>N09_1</t>
+  </si>
+  <si>
     <t>PI09</t>
   </si>
   <si>
-    <t>N01</t>
-  </si>
-  <si>
-    <t>N01_0</t>
-  </si>
-  <si>
-    <t>N01_1</t>
-  </si>
-  <si>
-    <t>N_post_C_0_0</t>
-  </si>
-  <si>
-    <t>N02</t>
-  </si>
-  <si>
-    <t>N02_0</t>
-  </si>
-  <si>
-    <t>N03_C</t>
-  </si>
-  <si>
-    <t>N03_C_0</t>
-  </si>
-  <si>
-    <t>N04</t>
-  </si>
-  <si>
-    <t>N_post_C_1_0</t>
-  </si>
-  <si>
-    <t>N04_0</t>
-  </si>
-  <si>
-    <t>N04_1</t>
-  </si>
-  <si>
-    <t>N05</t>
-  </si>
-  <si>
-    <t>N_post_C_1_1</t>
-  </si>
-  <si>
-    <t>N05_0</t>
-  </si>
-  <si>
-    <t>N05_1</t>
-  </si>
-  <si>
-    <t>N06_C</t>
-  </si>
-  <si>
-    <t>N06_C_0</t>
-  </si>
-  <si>
-    <t>N06_C_1</t>
-  </si>
-  <si>
-    <t>N_post_C_2_0</t>
-  </si>
-  <si>
-    <t>N07_0</t>
-  </si>
-  <si>
-    <t>N07_1</t>
-  </si>
-  <si>
-    <t>N08_C</t>
-  </si>
-  <si>
-    <t>N08_C_0</t>
-  </si>
-  <si>
-    <t>N08_C_1</t>
-  </si>
-  <si>
-    <t>N09</t>
-  </si>
-  <si>
-    <t>N09_0</t>
-  </si>
-  <si>
-    <t>N09_1</t>
-  </si>
-  <si>
-    <t>N_pre_C_0_0</t>
-  </si>
-  <si>
-    <t>N03</t>
-  </si>
-  <si>
-    <t>N_pre_C_1_0</t>
-  </si>
-  <si>
-    <t>N_pre_C_1_1</t>
-  </si>
-  <si>
-    <t>N06</t>
-  </si>
-  <si>
-    <t>N07</t>
-  </si>
-  <si>
-    <t>N08</t>
-  </si>
-  <si>
     <t>N10</t>
   </si>
   <si>
-    <t>Existing</t>
-  </si>
-  <si>
     <t>Segment</t>
   </si>
   <si>
@@ -661,22 +710,316 @@
   </si>
   <si>
     <t>N13</t>
+  </si>
+  <si>
+    <t>capacity</t>
+  </si>
+  <si>
+    <t>527617.1846909181</t>
+  </si>
+  <si>
+    <t>long term utilization</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>demand rampup</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>analysis start year</t>
+  </si>
+  <si>
+    <t>2020</t>
+  </si>
+  <si>
+    <t>operating life</t>
+  </si>
+  <si>
+    <t>50</t>
+  </si>
+  <si>
+    <t>installation months</t>
+  </si>
+  <si>
+    <t>36</t>
+  </si>
+  <si>
+    <t>TOPC</t>
+  </si>
+  <si>
+    <t>unit price</t>
+  </si>
+  <si>
+    <t>0.0</t>
+  </si>
+  <si>
+    <t>decay</t>
+  </si>
+  <si>
+    <t>support utilization</t>
+  </si>
+  <si>
+    <t>sunset years</t>
+  </si>
+  <si>
+    <t>commodity</t>
+  </si>
+  <si>
+    <t>name</t>
+  </si>
+  <si>
+    <t>Natural Gas-H2 Blend</t>
+  </si>
+  <si>
+    <t>unit</t>
+  </si>
+  <si>
+    <t>MMBTU</t>
+  </si>
+  <si>
+    <t>initial price</t>
+  </si>
+  <si>
+    <t>0.25</t>
+  </si>
+  <si>
+    <t>escalation</t>
+  </si>
+  <si>
+    <t>0.025</t>
+  </si>
+  <si>
+    <t>annual operating incentive</t>
+  </si>
+  <si>
+    <t>value</t>
+  </si>
+  <si>
+    <t>taxable</t>
+  </si>
+  <si>
+    <t>True</t>
+  </si>
+  <si>
+    <t>incidental revenue</t>
+  </si>
+  <si>
+    <t>credit card fees</t>
+  </si>
+  <si>
+    <t>sales tax</t>
+  </si>
+  <si>
+    <t>road tax</t>
+  </si>
+  <si>
+    <t>labor</t>
+  </si>
+  <si>
+    <t>rate</t>
+  </si>
+  <si>
+    <t>maintenance</t>
+  </si>
+  <si>
+    <t>rent</t>
+  </si>
+  <si>
+    <t>license and permit</t>
+  </si>
+  <si>
+    <t>non depr assets</t>
+  </si>
+  <si>
+    <t>end of proj sale non depr assets</t>
+  </si>
+  <si>
+    <t>installation cost</t>
+  </si>
+  <si>
+    <t>depr type</t>
+  </si>
+  <si>
+    <t>Straight line</t>
+  </si>
+  <si>
+    <t>depr period</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>depreciable</t>
+  </si>
+  <si>
+    <t>one time cap inct</t>
+  </si>
+  <si>
+    <t>MACRS</t>
+  </si>
+  <si>
+    <t>property tax and insurance</t>
+  </si>
+  <si>
+    <t>0.009</t>
+  </si>
+  <si>
+    <t>admin expense</t>
+  </si>
+  <si>
+    <t>0.005</t>
+  </si>
+  <si>
+    <t>tax loss carry forward years</t>
+  </si>
+  <si>
+    <t>capital gains tax rate</t>
+  </si>
+  <si>
+    <t>0.15</t>
+  </si>
+  <si>
+    <t>tax losses monetized</t>
+  </si>
+  <si>
+    <t>sell undepreciated cap</t>
+  </si>
+  <si>
+    <t>loan period if used</t>
+  </si>
+  <si>
+    <t>debt equity ratio of initial financing</t>
+  </si>
+  <si>
+    <t>0.62</t>
+  </si>
+  <si>
+    <t>debt interest rate</t>
+  </si>
+  <si>
+    <t>0.07</t>
+  </si>
+  <si>
+    <t>debt type</t>
+  </si>
+  <si>
+    <t>Revolving debt</t>
+  </si>
+  <si>
+    <t>total income tax rate</t>
+  </si>
+  <si>
+    <t>0.2574</t>
+  </si>
+  <si>
+    <t>cash onhand</t>
+  </si>
+  <si>
+    <t>general inflation rate</t>
+  </si>
+  <si>
+    <t>leverage after tax nominal discount rate</t>
+  </si>
+  <si>
+    <t>0.13</t>
+  </si>
+  <si>
+    <t>fraction of year operated</t>
+  </si>
+  <si>
+    <t>[0. 0. 0. 0. 1. 1. 1. 1. 1. 1. 1. 1. 1. 1. 1. 1. 1. 1. 1. 1. 1. 1. 1. 1.
+ 1. 1. 1. 1. 1. 1. 1. 1. 1. 1. 1. 1. 1. 1. 1. 1. 1. 1. 1. 1. 1. 1. 1. 1.
+ 1. 1. 1. 1. 1. 1.]</t>
+  </si>
+  <si>
+    <t>New pipe CapEx</t>
+  </si>
+  <si>
+    <t>cost</t>
+  </si>
+  <si>
+    <t>depr_type</t>
+  </si>
+  <si>
+    <t>depr_period</t>
+  </si>
+  <si>
+    <t>refurb</t>
+  </si>
+  <si>
+    <t>[0]</t>
+  </si>
+  <si>
+    <t>New compression capacity CapEx</t>
+  </si>
+  <si>
+    <t>53323460.926557705</t>
+  </si>
+  <si>
+    <t>Refurbished compressor capacity CapEx</t>
+  </si>
+  <si>
+    <t>50748077.07023712</t>
+  </si>
+  <si>
+    <t>Supply compressor CapEx</t>
+  </si>
+  <si>
+    <t>Meter &amp; regulator station modification CapEx</t>
+  </si>
+  <si>
+    <t>10486757.29473448</t>
+  </si>
+  <si>
+    <t>Valve replacement CapEx</t>
+  </si>
+  <si>
+    <t>24862120.0</t>
+  </si>
+  <si>
+    <t>Original network residual value</t>
+  </si>
+  <si>
+    <t>Gas pressure regulation and metering station</t>
+  </si>
+  <si>
+    <t>Compressor fuel</t>
+  </si>
+  <si>
+    <t>{'2048': np.float64(65.4655149438955), '2049': np.float64(67.10215281749288), '2050': np.float64(68.77970663793019), '2051': np.float64(70.49919930387846), '2052': np.float64(72.2616792864754), '2053': np.float64(74.06822126863727), '2054': np.float64(75.9199268003532), '2055': np.float64(77.81792497036201), '2056': np.float64(79.76337309462106), '2057': np.float64(81.75745742198659), '2058': np.float64(83.80139385753625), '2059': np.float64(85.89642870397464), '2060': np.float64(88.04383942157399), '2061': np.float64(90.24493540711335), '2062': np.float64(92.50105879229116), '2063': np.float64(94.81358526209844), '2064': np.float64(97.1839248936509), '2065': np.float64(99.61352301599216), '2066': np.float64(102.10386109139195), '2067': np.float64(104.65645761867674), '2068': np.float64(107.27286905914366), '2069': np.float64(109.95469078562223), '2070': np.float64(112.70355805526277), '2071': np.float64(115.52114700664434), '2072': np.float64(118.40917568181044), '2073': np.float64(121.36940507385569), '2074': np.float64(124.40364020070207), '2075': np.float64(127.51373120571961), '2076': np.float64(130.7015744858626), '2077': np.float64(133.96911384800913), '2078': np.float64(137.31834169420938), '2079': np.float64(140.75130023656456), '2080': np.float64(144.27008274247868), '2081': np.float64(147.87683481104065), '2082': np.float64(151.57375568131664), '2020': np.float64(32.790222028526316), '2021': np.float64(33.60997757923947), '2022': np.float64(34.450227018720454), '2023': np.float64(35.31148269418846), '2024': np.float64(36.19426976154317), '2025': np.float64(37.099126505581744), '2026': np.float64(38.02660466822129), '2027': np.float64(38.97726978492682), '2028': np.float64(39.95170152954998), '2029': np.float64(40.95049406778873), '2030': np.float64(41.97425641948344), '2031': np.float64(43.023612829970524), '2032': np.float64(44.09920315071979), '2033': np.float64(45.20168322948777), '2034': np.float64(46.33172531022497), '2035': np.float64(47.490018442980585), '2036': np.float64(48.6772689040551), '2037': np.float64(49.89420062665647), '2038': np.float64(51.14155564232288), '2039': np.float64(52.42009453338094), '2040': np.float64(53.73059689671546), '2041': np.float64(55.07386181913335), '2042': np.float64(56.45070836461168), '2043': np.float64(57.861976073726964), '2044': np.float64(59.30852547557013), '2045': np.float64(60.79123861245938), '2046': np.float64(62.31101957777086), '2047': np.float64(63.868795067215125)}</t>
+  </si>
+  <si>
+    <t>usage</t>
+  </si>
+  <si>
+    <t>0.018297410777423095</t>
+  </si>
+  <si>
+    <t>Compressor fuel (electric)</t>
+  </si>
+  <si>
+    <t>Supply commpressor fuel (electric)</t>
+  </si>
+  <si>
+    <t>Supply commpressor fuel</t>
+  </si>
+  <si>
+    <t>In-line inspection</t>
+  </si>
+  <si>
+    <t>3277333.333333336</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+  <fonts count="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -692,7 +1035,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -700,32 +1043,14 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1039,14 +1364,14 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B26"/>
+  <dimension ref="A1:B34"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
-      <c r="A1" s="2" t="s">
+      <c r="A1" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" t="s">
         <v>2</v>
       </c>
     </row>
@@ -1055,28 +1380,28 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>28</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B3" t="s">
-        <v>29</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B4" t="s">
-        <v>30</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B5">
         <v>1</v>
@@ -1084,7 +1409,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B6">
         <v>1</v>
@@ -1092,7 +1417,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B7">
         <v>1</v>
@@ -1100,15 +1425,15 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B8" t="s">
-        <v>31</v>
+        <v>13</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="B9">
         <v>1</v>
@@ -1116,7 +1441,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="B10">
         <v>7.39</v>
@@ -1124,7 +1449,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B11">
         <v>4.40756</v>
@@ -1132,7 +1457,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B12">
         <v>0.07000000000000001</v>
@@ -1140,7 +1465,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="B13">
         <v>3.325</v>
@@ -1148,63 +1473,63 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B14" t="s">
-        <v>32</v>
+        <v>20</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="B15" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="B16" t="s">
-        <v>30</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" t="s">
-        <v>18</v>
-      </c>
-      <c r="B17" t="b">
-        <v>1</v>
+        <v>24</v>
+      </c>
+      <c r="B17" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" t="s">
-        <v>19</v>
-      </c>
-      <c r="B18" t="s">
-        <v>34</v>
+        <v>26</v>
+      </c>
+      <c r="B18">
+        <v>3</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="B19">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" t="s">
-        <v>21</v>
-      </c>
-      <c r="B20">
+        <v>28</v>
+      </c>
+      <c r="B20" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="B21" t="b">
         <v>0</v>
@@ -1212,39 +1537,100 @@
     </row>
     <row r="22" spans="1:2">
       <c r="A22" t="s">
-        <v>23</v>
-      </c>
-      <c r="B22" t="b">
-        <v>0</v>
+        <v>30</v>
+      </c>
+      <c r="B22">
+        <v>0.78</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="B23">
-        <v>0.78</v>
+        <v>0.88</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="B24">
-        <v>0.88</v>
+        <v>0.357</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" t="s">
-        <v>26</v>
-      </c>
-      <c r="B25">
-        <v>0.357</v>
+        <v>33</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" t="s">
-        <v>27</v>
+        <v>34</v>
+      </c>
+      <c r="B26">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2">
+      <c r="A27" t="s">
+        <v>35</v>
+      </c>
+      <c r="B27">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2">
+      <c r="A28" t="s">
+        <v>36</v>
+      </c>
+      <c r="B28" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2">
+      <c r="A29" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2">
+      <c r="A30" t="s">
+        <v>39</v>
+      </c>
+      <c r="B30" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2">
+      <c r="A31" t="s">
+        <v>40</v>
+      </c>
+      <c r="B31" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2">
+      <c r="A32" t="s">
+        <v>41</v>
+      </c>
+      <c r="B32" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2">
+      <c r="A33" t="s">
+        <v>43</v>
+      </c>
+      <c r="B33" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2">
+      <c r="A34" t="s">
+        <v>45</v>
+      </c>
+      <c r="B34">
+        <v>20</v>
       </c>
     </row>
   </sheetData>
@@ -1254,268 +1640,268 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H58"/>
+  <dimension ref="A1:H66"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="B1" s="2" t="s">
+      <c r="A1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B1" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="2" t="s">
-        <v>36</v>
+      <c r="C1" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="B2">
-        <v>0.7668143772587662</v>
+        <v>0.753522391874012</v>
       </c>
       <c r="C2" t="s">
-        <v>69</v>
+        <v>49</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="B3">
         <v>0</v>
       </c>
       <c r="C3" t="s">
-        <v>69</v>
+        <v>49</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="B4">
-        <v>0.04428606052510944</v>
+        <v>0.03751327044830297</v>
       </c>
       <c r="C4" t="s">
-        <v>69</v>
+        <v>49</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="B5">
-        <v>0.03538808973054117</v>
+        <v>0.03570147748828843</v>
       </c>
       <c r="C5" t="s">
-        <v>69</v>
+        <v>49</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="B6">
         <v>0</v>
       </c>
       <c r="C6" t="s">
-        <v>69</v>
+        <v>49</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="B7">
-        <v>0.00731271664963476</v>
+        <v>0.007377476174416123</v>
       </c>
       <c r="C7" t="s">
-        <v>69</v>
+        <v>49</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="B8">
-        <v>0.01733706938755091</v>
+        <v>0.01749060198404436</v>
       </c>
       <c r="C8" t="s">
-        <v>69</v>
+        <v>49</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="B9">
         <v>0</v>
       </c>
       <c r="C9" t="s">
-        <v>69</v>
+        <v>49</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" t="s">
-        <v>45</v>
+        <v>57</v>
       </c>
       <c r="B10">
         <v>0.01701801172198348</v>
       </c>
       <c r="C10" t="s">
-        <v>69</v>
+        <v>49</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" t="s">
-        <v>46</v>
+        <v>58</v>
       </c>
       <c r="B11">
-        <v>0.6050741821982345</v>
+        <v>0.5999761619388537</v>
       </c>
       <c r="C11" t="s">
-        <v>69</v>
+        <v>49</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" t="s">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c r="B12">
         <v>0</v>
       </c>
       <c r="C12" t="s">
-        <v>69</v>
+        <v>49</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" t="s">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="B13">
         <v>0</v>
       </c>
       <c r="C13" t="s">
-        <v>69</v>
+        <v>49</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" t="s">
-        <v>49</v>
+        <v>61</v>
       </c>
       <c r="B14">
         <v>0</v>
       </c>
       <c r="C14" t="s">
-        <v>69</v>
+        <v>49</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" t="s">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="B15">
-        <v>0.00606245681164367</v>
+        <v>0</v>
       </c>
       <c r="C15" t="s">
-        <v>69</v>
+        <v>49</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" t="s">
-        <v>51</v>
+        <v>63</v>
       </c>
       <c r="B16">
-        <v>0.03032586155389432</v>
+        <v>0</v>
       </c>
       <c r="C16" t="s">
-        <v>69</v>
+        <v>49</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" t="s">
-        <v>52</v>
+        <v>64</v>
       </c>
       <c r="B17">
-        <v>0.004009928680173636</v>
+        <v>0.005844294672351176</v>
       </c>
       <c r="C17" t="s">
-        <v>69</v>
+        <v>49</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="B18">
-        <v>4.40756</v>
+        <v>0.02863813440945233</v>
       </c>
       <c r="C18" t="s">
-        <v>70</v>
+        <v>49</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" t="s">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="B19">
-        <v>7.39</v>
+        <v>0.003962963036319368</v>
       </c>
       <c r="C19" t="s">
-        <v>69</v>
+        <v>49</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" t="s">
-        <v>55</v>
+        <v>67</v>
       </c>
       <c r="B20">
-        <v>32.79022202852632</v>
+        <v>4.40756</v>
       </c>
       <c r="C20" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21" t="s">
-        <v>56</v>
+        <v>69</v>
       </c>
       <c r="B21">
-        <v>527617.1846909181</v>
+        <v>7.39</v>
       </c>
       <c r="C21" t="s">
-        <v>71</v>
+        <v>49</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22" t="s">
-        <v>57</v>
+        <v>70</v>
       </c>
       <c r="B22">
-        <v>21984.04936212159</v>
+        <v>32.79022202852632</v>
       </c>
       <c r="C22" t="s">
-        <v>72</v>
+        <v>49</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" t="s">
-        <v>58</v>
+        <v>71</v>
       </c>
       <c r="B23">
-        <v>0</v>
+        <v>527617.1846909181</v>
       </c>
       <c r="C23" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" t="s">
-        <v>58</v>
+        <v>73</v>
       </c>
       <c r="B24">
-        <v>0</v>
+        <v>21984.04936212159</v>
       </c>
       <c r="C24" t="s">
         <v>74</v>
@@ -1523,396 +1909,439 @@
     </row>
     <row r="25" spans="1:3">
       <c r="A25" t="s">
-        <v>59</v>
+        <v>75</v>
       </c>
       <c r="B25">
-        <v>4</v>
+        <v>0</v>
+      </c>
+      <c r="C25" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" t="s">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="B26">
-        <v>33454.57386032275</v>
+        <v>0</v>
       </c>
       <c r="C26" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" t="s">
-        <v>61</v>
+        <v>78</v>
       </c>
       <c r="B27">
-        <v>9736.059007555912</v>
-      </c>
-      <c r="C27" t="s">
-        <v>71</v>
+        <v>3</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" t="s">
-        <v>61</v>
+        <v>79</v>
       </c>
       <c r="B28">
-        <v>405.6691253148297</v>
+        <v>30086.07593590436</v>
       </c>
       <c r="C28" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" t="s">
-        <v>62</v>
+        <v>81</v>
       </c>
       <c r="B29">
-        <v>0</v>
+        <v>9654.028361517236</v>
       </c>
       <c r="C29" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
     </row>
     <row r="30" spans="1:3">
       <c r="A30" t="s">
-        <v>63</v>
+        <v>81</v>
       </c>
       <c r="B30">
-        <v>0</v>
+        <v>402.2511817298848</v>
       </c>
       <c r="C30" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
     </row>
     <row r="31" spans="1:3">
       <c r="A31" t="s">
-        <v>64</v>
+        <v>82</v>
       </c>
       <c r="B31">
-        <v>63508158.52955821</v>
+        <v>0</v>
       </c>
       <c r="C31" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
     </row>
     <row r="32" spans="1:3">
       <c r="A32" t="s">
-        <v>65</v>
+        <v>84</v>
       </c>
       <c r="B32">
+        <v>0</v>
+      </c>
+      <c r="C32" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" t="s">
+        <v>86</v>
+      </c>
+      <c r="B33">
+        <v>53323460.9265577</v>
+      </c>
+      <c r="C33" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" t="s">
+        <v>87</v>
+      </c>
+      <c r="B34">
         <v>50748077.07023712</v>
       </c>
-      <c r="C32" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="33" spans="1:8">
-      <c r="A33" t="s">
-        <v>66</v>
-      </c>
-      <c r="B33">
+      <c r="C34" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" t="s">
+        <v>88</v>
+      </c>
+      <c r="B35">
         <v>10486757.29473448</v>
       </c>
-      <c r="C33" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="34" spans="1:8">
-      <c r="A34" t="s">
-        <v>67</v>
-      </c>
-      <c r="B34">
+      <c r="C35" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" t="s">
+        <v>89</v>
+      </c>
+      <c r="B36">
         <v>24862120</v>
       </c>
-      <c r="C34" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="35" spans="1:8">
-      <c r="A35" t="s">
-        <v>68</v>
-      </c>
-      <c r="B35">
+      <c r="C36" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" t="s">
+        <v>90</v>
+      </c>
+      <c r="B37">
+        <v>0</v>
+      </c>
+      <c r="C37" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" t="s">
+        <v>91</v>
+      </c>
+      <c r="B38">
+        <v>0</v>
+      </c>
+      <c r="C38" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" t="s">
+        <v>92</v>
+      </c>
+      <c r="B39">
         <v>100</v>
       </c>
-      <c r="C35" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="39" spans="1:8">
-      <c r="A39" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="40" spans="1:8">
-      <c r="A40" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="B40" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="C40" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="D40" s="2" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="41" spans="1:8">
-      <c r="A41">
+      <c r="C39" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" t="s">
+        <v>94</v>
+      </c>
+      <c r="B40">
+        <v>0.07391174439093808</v>
+      </c>
+      <c r="C40" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" t="s">
+        <v>96</v>
+      </c>
+      <c r="B41">
+        <v>0.01423394386926665</v>
+      </c>
+      <c r="C41" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" t="s">
+        <v>99</v>
+      </c>
+      <c r="B47" t="s">
+        <v>100</v>
+      </c>
+      <c r="C47" t="s">
+        <v>101</v>
+      </c>
+      <c r="D47" t="s">
+        <v>102</v>
+      </c>
+      <c r="E47" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48">
         <v>650</v>
       </c>
-      <c r="B41">
+      <c r="B48">
         <v>400.0000000000002</v>
       </c>
-      <c r="C41" t="s">
-        <v>84</v>
-      </c>
-      <c r="D41" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="45" spans="1:8">
-      <c r="A45" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="46" spans="1:8">
-      <c r="A46" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="B46" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="C46" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="D46" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="E46" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="F46" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="G46" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="H46" s="2" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="50" spans="1:8">
-      <c r="A50" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="51" spans="1:8">
-      <c r="A51" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="B51" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="C51" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="D51" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="E51" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="F51" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="G51" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="H51" s="2" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="52" spans="1:8">
-      <c r="A52" t="s">
-        <v>101</v>
-      </c>
-      <c r="B52">
-        <v>7.842291708880055</v>
-      </c>
-      <c r="C52">
-        <v>0</v>
-      </c>
-      <c r="D52">
-        <v>10516.67002744233</v>
-      </c>
-      <c r="E52">
-        <v>18311088.15709077</v>
-      </c>
-      <c r="F52">
-        <v>0</v>
-      </c>
-      <c r="G52">
-        <v>74.95491554868013</v>
-      </c>
-      <c r="H52">
-        <v>0</v>
+      <c r="C48" t="s">
+        <v>104</v>
+      </c>
+      <c r="D48" t="s">
+        <v>105</v>
       </c>
     </row>
     <row r="53" spans="1:8">
       <c r="A53" t="s">
-        <v>102</v>
-      </c>
-      <c r="B53">
-        <v>7.168805858468696</v>
-      </c>
-      <c r="C53">
-        <v>12.5</v>
-      </c>
-      <c r="D53">
-        <v>0</v>
-      </c>
-      <c r="E53">
-        <v>0</v>
-      </c>
-      <c r="F53">
-        <v>16916025.69007904</v>
-      </c>
-      <c r="G53">
-        <v>68.51788452321429</v>
-      </c>
-      <c r="H53">
-        <v>0</v>
+        <v>106</v>
       </c>
     </row>
     <row r="54" spans="1:8">
       <c r="A54" t="s">
-        <v>103</v>
-      </c>
-      <c r="B54">
-        <v>6.688404352356296</v>
-      </c>
-      <c r="C54">
+        <v>99</v>
+      </c>
+      <c r="B54" t="s">
+        <v>100</v>
+      </c>
+      <c r="C54" t="s">
+        <v>107</v>
+      </c>
+      <c r="D54" t="s">
+        <v>102</v>
+      </c>
+      <c r="E54" t="s">
+        <v>108</v>
+      </c>
+      <c r="F54" t="s">
+        <v>109</v>
+      </c>
+      <c r="G54" t="s">
+        <v>110</v>
+      </c>
+      <c r="H54" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8">
+      <c r="A59" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8">
+      <c r="A60" t="s">
+        <v>113</v>
+      </c>
+      <c r="B60" t="s">
+        <v>114</v>
+      </c>
+      <c r="C60" t="s">
+        <v>115</v>
+      </c>
+      <c r="D60" t="s">
+        <v>116</v>
+      </c>
+      <c r="E60" t="s">
+        <v>117</v>
+      </c>
+      <c r="F60" t="s">
+        <v>118</v>
+      </c>
+      <c r="G60" t="s">
+        <v>119</v>
+      </c>
+      <c r="H60" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8">
+      <c r="A61" t="s">
+        <v>121</v>
+      </c>
+      <c r="B61">
+        <v>7.63663511154234</v>
+      </c>
+      <c r="C61">
         <v>0</v>
       </c>
-      <c r="D54">
-        <v>8969.284004596841</v>
-      </c>
-      <c r="E54">
-        <v>16550382.92341388</v>
-      </c>
-      <c r="F54">
+      <c r="D61">
+        <v>10240.88041728051</v>
+      </c>
+      <c r="E61">
+        <v>17995750.75756607</v>
+      </c>
+      <c r="F61">
         <v>0</v>
       </c>
-      <c r="G54">
-        <v>63.92631159315608</v>
-      </c>
-      <c r="H54">
+      <c r="G61">
+        <v>72.98929459785241</v>
+      </c>
+      <c r="H61">
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:8">
-      <c r="A55" t="s">
-        <v>104</v>
-      </c>
-      <c r="B55">
-        <v>4.846034835883339</v>
-      </c>
-      <c r="C55">
+    <row r="62" spans="1:8">
+      <c r="A62" t="s">
+        <v>122</v>
+      </c>
+      <c r="B62">
+        <v>6.96226671748084</v>
+      </c>
+      <c r="C62">
+        <v>12.5</v>
+      </c>
+      <c r="D62">
         <v>0</v>
       </c>
-      <c r="D55">
-        <v>6498.629635616275</v>
-      </c>
-      <c r="E55">
-        <v>13782384.48884103</v>
-      </c>
-      <c r="F55">
+      <c r="E62">
         <v>0</v>
       </c>
-      <c r="G55">
-        <v>46.31734515285845</v>
-      </c>
-      <c r="H55">
+      <c r="F62">
+        <v>16916025.69007904</v>
+      </c>
+      <c r="G62">
+        <v>66.54382841245881</v>
+      </c>
+      <c r="H62">
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:8">
-      <c r="A56" t="s">
-        <v>105</v>
-      </c>
-      <c r="B56">
-        <v>4.808005909718052</v>
-      </c>
-      <c r="C56">
+    <row r="63" spans="1:8">
+      <c r="A63" t="s">
+        <v>123</v>
+      </c>
+      <c r="B63">
+        <v>9.394865353149434</v>
+      </c>
+      <c r="C63">
+        <v>0</v>
+      </c>
+      <c r="D63">
+        <v>12598.70233588045</v>
+      </c>
+      <c r="E63">
+        <v>20713070.39647818</v>
+      </c>
+      <c r="F63">
+        <v>0</v>
+      </c>
+      <c r="G63">
+        <v>89.79407618045634</v>
+      </c>
+      <c r="H63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8">
+      <c r="A64" t="s">
+        <v>124</v>
+      </c>
+      <c r="B64">
+        <v>7.333001639097953</v>
+      </c>
+      <c r="C64">
         <v>12.5</v>
       </c>
-      <c r="D56">
+      <c r="D64">
         <v>0</v>
       </c>
-      <c r="E56">
+      <c r="E64">
         <v>0</v>
       </c>
-      <c r="F56">
+      <c r="F64">
         <v>16916025.69007904</v>
       </c>
-      <c r="G56">
-        <v>45.95387296195558</v>
-      </c>
-      <c r="H56">
+      <c r="G64">
+        <v>70.0872320210356</v>
+      </c>
+      <c r="H64">
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:8">
-      <c r="A57" t="s">
-        <v>106</v>
-      </c>
-      <c r="B57">
-        <v>5.570379407217869</v>
-      </c>
-      <c r="C57">
+    <row r="65" spans="1:8">
+      <c r="A65" t="s">
+        <v>125</v>
+      </c>
+      <c r="B65">
+        <v>5.403717455924144</v>
+      </c>
+      <c r="C65">
         <v>0</v>
       </c>
-      <c r="D57">
-        <v>7469.990192667306</v>
-      </c>
-      <c r="E57">
-        <v>14864302.96021254</v>
-      </c>
-      <c r="F57">
+      <c r="D65">
+        <v>7246.493182743396</v>
+      </c>
+      <c r="E65">
+        <v>14614639.77251345</v>
+      </c>
+      <c r="F65">
         <v>0</v>
       </c>
-      <c r="G57">
-        <v>53.24047275228795</v>
-      </c>
-      <c r="H57">
+      <c r="G65">
+        <v>51.64755413256176</v>
+      </c>
+      <c r="H65">
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:8">
-      <c r="A58" t="s">
-        <v>107</v>
-      </c>
-      <c r="B58">
-        <v>5.519933606813229</v>
-      </c>
-      <c r="C58">
+    <row r="66" spans="1:8">
+      <c r="A66" t="s">
+        <v>126</v>
+      </c>
+      <c r="B66">
+        <v>5.355760959235239</v>
+      </c>
+      <c r="C66">
         <v>12.5</v>
       </c>
-      <c r="D58">
+      <c r="D66">
         <v>0</v>
       </c>
-      <c r="E58">
+      <c r="E66">
         <v>0</v>
       </c>
-      <c r="F58">
+      <c r="F66">
         <v>16916025.69007904</v>
       </c>
-      <c r="G58">
-        <v>52.75832278267718</v>
-      </c>
-      <c r="H58">
+      <c r="G66">
+        <v>51.18919638551989</v>
+      </c>
+      <c r="H66">
         <v>0</v>
       </c>
     </row>
@@ -1923,63 +2352,63 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R29"/>
+  <dimension ref="A1:R28"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:18">
-      <c r="A1" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="J1" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="K1" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="L1" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="M1" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="N1" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="O1" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="P1" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="Q1" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="R1" s="2" t="s">
-        <v>123</v>
+      <c r="A1" t="s">
+        <v>127</v>
+      </c>
+      <c r="B1" t="s">
+        <v>128</v>
+      </c>
+      <c r="C1" t="s">
+        <v>129</v>
+      </c>
+      <c r="D1" t="s">
+        <v>130</v>
+      </c>
+      <c r="E1" t="s">
+        <v>131</v>
+      </c>
+      <c r="F1" t="s">
+        <v>132</v>
+      </c>
+      <c r="G1" t="s">
+        <v>133</v>
+      </c>
+      <c r="H1" t="s">
+        <v>102</v>
+      </c>
+      <c r="I1" t="s">
+        <v>134</v>
+      </c>
+      <c r="J1" t="s">
+        <v>135</v>
+      </c>
+      <c r="K1" t="s">
+        <v>136</v>
+      </c>
+      <c r="L1" t="s">
+        <v>100</v>
+      </c>
+      <c r="M1" t="s">
+        <v>137</v>
+      </c>
+      <c r="N1" t="s">
+        <v>138</v>
+      </c>
+      <c r="O1" t="s">
+        <v>139</v>
+      </c>
+      <c r="P1" t="s">
+        <v>140</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>141</v>
+      </c>
+      <c r="R1" t="s">
+        <v>142</v>
       </c>
     </row>
     <row r="2" spans="1:18">
@@ -1987,31 +2416,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>124</v>
+        <v>143</v>
       </c>
       <c r="C2" t="s">
-        <v>152</v>
+        <v>144</v>
       </c>
       <c r="D2" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="E2" t="s">
-        <v>188</v>
+        <v>146</v>
       </c>
       <c r="F2">
-        <v>46.26840324111094</v>
+        <v>46.26210605839778</v>
       </c>
       <c r="G2">
         <v>650</v>
       </c>
       <c r="H2" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="I2">
         <v>9.525</v>
       </c>
       <c r="J2" t="s">
-        <v>84</v>
+        <v>104</v>
       </c>
       <c r="K2">
         <v>8.758481331682836</v>
@@ -2026,16 +2455,16 @@
         <v>8700000</v>
       </c>
       <c r="O2">
-        <v>8400980.744238859</v>
+        <v>8404437.121807171</v>
       </c>
       <c r="P2">
-        <v>20.72262859651975</v>
+        <v>21.10628589612484</v>
       </c>
       <c r="Q2">
-        <v>0.01554896299071758</v>
+        <v>0.01592675267498209</v>
       </c>
       <c r="R2">
-        <v>47.10940500122411</v>
+        <v>46.83376796391618</v>
       </c>
     </row>
     <row r="3" spans="1:18">
@@ -2043,31 +2472,31 @@
         <v>0</v>
       </c>
       <c r="B3" t="s">
-        <v>125</v>
+        <v>147</v>
       </c>
       <c r="C3" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="D3" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="E3" t="s">
-        <v>188</v>
+        <v>146</v>
       </c>
       <c r="F3">
-        <v>46.26841413721092</v>
+        <v>46.26212276767984</v>
       </c>
       <c r="G3">
         <v>650</v>
       </c>
       <c r="H3" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="I3">
         <v>9.525</v>
       </c>
       <c r="J3" t="s">
-        <v>84</v>
+        <v>104</v>
       </c>
       <c r="K3">
         <v>8.758481331682836</v>
@@ -2079,19 +2508,19 @@
         <v>8.284946666666665</v>
       </c>
       <c r="N3">
-        <v>8400980.744238859</v>
+        <v>8404437.121807171</v>
       </c>
       <c r="O3">
-        <v>8091531.137787693</v>
+        <v>8098822.381386424</v>
       </c>
       <c r="P3">
-        <v>20.73860037866104</v>
+        <v>21.85067833231916</v>
       </c>
       <c r="Q3">
-        <v>0.01557782402519739</v>
+        <v>0.01650986885054506</v>
       </c>
       <c r="R3">
-        <v>47.95495305851576</v>
+        <v>47.65248738555071</v>
       </c>
     </row>
     <row r="4" spans="1:18">
@@ -2099,31 +2528,31 @@
         <v>0</v>
       </c>
       <c r="B4" t="s">
-        <v>126</v>
+        <v>149</v>
       </c>
       <c r="C4" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="D4" t="s">
-        <v>180</v>
+        <v>150</v>
       </c>
       <c r="E4" t="s">
-        <v>188</v>
+        <v>146</v>
       </c>
       <c r="F4">
-        <v>46.26842496231473</v>
+        <v>46.26210213802118</v>
       </c>
       <c r="G4">
         <v>650</v>
       </c>
       <c r="H4" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="I4">
         <v>9.525</v>
       </c>
       <c r="J4" t="s">
-        <v>84</v>
+        <v>104</v>
       </c>
       <c r="K4">
         <v>8.758481331682836</v>
@@ -2135,19 +2564,19 @@
         <v>5.178091666666666</v>
       </c>
       <c r="N4">
-        <v>8091531.137787693</v>
+        <v>8098822.381386424</v>
       </c>
       <c r="O4">
-        <v>7892286.172675607</v>
+        <v>7902201.653379492</v>
       </c>
       <c r="P4">
-        <v>20.7486089295085</v>
+        <v>22.35927344993096</v>
       </c>
       <c r="Q4">
-        <v>0.01559641968457603</v>
+        <v>0.0169085742525263</v>
       </c>
       <c r="R4">
-        <v>48.52544954933388</v>
+        <v>48.20388633158205</v>
       </c>
     </row>
     <row r="5" spans="1:18">
@@ -2155,31 +2584,31 @@
         <v>0</v>
       </c>
       <c r="B5" t="s">
-        <v>127</v>
+        <v>151</v>
       </c>
       <c r="C5" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="D5" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="E5" t="s">
-        <v>188</v>
+        <v>146</v>
       </c>
       <c r="F5">
-        <v>46.11430321568965</v>
+        <v>46.11132754214792</v>
       </c>
       <c r="G5">
         <v>650</v>
       </c>
       <c r="H5" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="I5">
         <v>9.525</v>
       </c>
       <c r="J5" t="s">
-        <v>84</v>
+        <v>104</v>
       </c>
       <c r="K5">
         <v>8.758481331682836</v>
@@ -2194,16 +2623,16 @@
         <v>8758481.331682835</v>
       </c>
       <c r="O5">
-        <v>8648934.335705761</v>
+        <v>8650145.275655651</v>
       </c>
       <c r="P5">
-        <v>20.48742402300153</v>
+        <v>20.47830660971497</v>
       </c>
       <c r="Q5">
-        <v>0.01535929092801148</v>
+        <v>0.01543708635105698</v>
       </c>
       <c r="R5">
-        <v>46.46512433400179</v>
+        <v>46.20714113686624</v>
       </c>
     </row>
     <row r="6" spans="1:18">
@@ -2211,31 +2640,31 @@
         <v>0</v>
       </c>
       <c r="B6" t="s">
-        <v>128</v>
+        <v>154</v>
       </c>
       <c r="C6" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="D6" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E6" t="s">
-        <v>188</v>
+        <v>146</v>
       </c>
       <c r="F6">
-        <v>46.11430363662723</v>
+        <v>46.11132756857262</v>
       </c>
       <c r="G6">
         <v>650</v>
       </c>
       <c r="H6" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="I6">
         <v>9.525</v>
       </c>
       <c r="J6" t="s">
-        <v>84</v>
+        <v>104</v>
       </c>
       <c r="K6">
         <v>8.758481331682836</v>
@@ -2247,19 +2676,19 @@
         <v>9.320565</v>
       </c>
       <c r="N6">
-        <v>8648934.335705761</v>
+        <v>8650145.275655651</v>
       </c>
       <c r="O6">
-        <v>8312110.789706063</v>
+        <v>8317246.107158598</v>
       </c>
       <c r="P6">
-        <v>20.50479538940009</v>
+        <v>21.24349364138911</v>
       </c>
       <c r="Q6">
-        <v>0.01539042169475343</v>
+        <v>0.01603625807862616</v>
       </c>
       <c r="R6">
-        <v>47.34693348960434</v>
+        <v>47.06250602263852</v>
       </c>
     </row>
     <row r="7" spans="1:18">
@@ -2267,31 +2696,31 @@
         <v>0</v>
       </c>
       <c r="B7" t="s">
-        <v>129</v>
+        <v>156</v>
       </c>
       <c r="C7" t="s">
+        <v>155</v>
+      </c>
+      <c r="D7" t="s">
         <v>157</v>
       </c>
-      <c r="D7" t="s">
-        <v>181</v>
-      </c>
       <c r="E7" t="s">
-        <v>188</v>
+        <v>146</v>
       </c>
       <c r="F7">
-        <v>46.1143042906361</v>
+        <v>46.11132760916916</v>
       </c>
       <c r="G7">
         <v>650</v>
       </c>
       <c r="H7" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="I7">
         <v>9.525</v>
       </c>
       <c r="J7" t="s">
-        <v>84</v>
+        <v>104</v>
       </c>
       <c r="K7">
         <v>8.758481331682836</v>
@@ -2303,19 +2732,19 @@
         <v>9.320565</v>
       </c>
       <c r="N7">
-        <v>8312110.789706063</v>
+        <v>8317246.107158598</v>
       </c>
       <c r="O7">
-        <v>7961828.336791218</v>
+        <v>7971388.272378965</v>
       </c>
       <c r="P7">
-        <v>20.52221220228204</v>
+        <v>22.10534842091557</v>
       </c>
       <c r="Q7">
-        <v>0.01542235930207861</v>
+        <v>0.01671146044200318</v>
       </c>
       <c r="R7">
-        <v>48.32402383795556</v>
+        <v>48.00768461589161</v>
       </c>
     </row>
     <row r="8" spans="1:18">
@@ -2323,31 +2752,31 @@
         <v>1</v>
       </c>
       <c r="B8" t="s">
-        <v>130</v>
+        <v>158</v>
       </c>
       <c r="C8" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D8" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E8" t="s">
-        <v>188</v>
+        <v>146</v>
       </c>
       <c r="F8">
-        <v>45.97273564796909</v>
+        <v>45.97381433229792</v>
       </c>
       <c r="G8">
         <v>650</v>
       </c>
       <c r="H8" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="I8">
         <v>9.525</v>
       </c>
       <c r="J8" t="s">
-        <v>84</v>
+        <v>104</v>
       </c>
       <c r="K8">
         <v>8.758481331682836</v>
@@ -2362,16 +2791,16 @@
         <v>8758481.331682835</v>
       </c>
       <c r="O8">
-        <v>8410967.683713766</v>
+        <v>8414863.001234222</v>
       </c>
       <c r="P8">
-        <v>20.47431857876862</v>
+        <v>20.95046533062455</v>
       </c>
       <c r="Q8">
-        <v>0.01536210202505038</v>
+        <v>0.01580847438533773</v>
       </c>
       <c r="R8">
-        <v>47.08293511776323</v>
+        <v>46.80663924514229</v>
       </c>
     </row>
     <row r="9" spans="1:18">
@@ -2379,31 +2808,31 @@
         <v>1</v>
       </c>
       <c r="B9" t="s">
-        <v>131</v>
+        <v>161</v>
       </c>
       <c r="C9" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="D9" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="E9" t="s">
-        <v>188</v>
+        <v>146</v>
       </c>
       <c r="F9">
-        <v>45.97273566854484</v>
+        <v>45.97381433469958</v>
       </c>
       <c r="G9">
         <v>650</v>
       </c>
       <c r="H9" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="I9">
         <v>9.525</v>
       </c>
       <c r="J9" t="s">
-        <v>84</v>
+        <v>104</v>
       </c>
       <c r="K9">
         <v>8.758481331682836</v>
@@ -2415,19 +2844,19 @@
         <v>9.786593249999999</v>
       </c>
       <c r="N9">
-        <v>8410967.683713766</v>
+        <v>8414863.001234222</v>
       </c>
       <c r="O9">
-        <v>8049296.565045817</v>
+        <v>8057594.965673572</v>
       </c>
       <c r="P9">
-        <v>20.49263925874537</v>
+        <v>21.81856883129615</v>
       </c>
       <c r="Q9">
-        <v>0.0153953477811797</v>
+        <v>0.01648850704734872</v>
       </c>
       <c r="R9">
-        <v>48.07420206244507</v>
+        <v>47.76653656583674</v>
       </c>
     </row>
     <row r="10" spans="1:18">
@@ -2435,55 +2864,55 @@
         <v>1</v>
       </c>
       <c r="B10" t="s">
-        <v>132</v>
+        <v>163</v>
       </c>
       <c r="C10" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="D10" t="s">
-        <v>182</v>
+        <v>164</v>
       </c>
       <c r="E10" t="s">
-        <v>188</v>
+        <v>146</v>
       </c>
       <c r="F10">
-        <v>37.86007548776315</v>
+        <v>37.86115406970113</v>
       </c>
       <c r="G10">
         <v>650</v>
       </c>
       <c r="H10" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="I10">
         <v>9.525</v>
       </c>
       <c r="J10" t="s">
-        <v>84</v>
+        <v>104</v>
       </c>
       <c r="K10">
         <v>8.758481331682836</v>
       </c>
       <c r="L10">
-        <v>11.83333333333334</v>
+        <v>16.16666666666667</v>
       </c>
       <c r="M10">
-        <v>7.35289016666667</v>
+        <v>10.04549783333334</v>
       </c>
       <c r="N10">
-        <v>8049296.565045817</v>
+        <v>8057594.965673572</v>
       </c>
       <c r="O10">
-        <v>7856753.446551932</v>
+        <v>7796881.49500763</v>
       </c>
       <c r="P10">
-        <v>16.88773231140672</v>
+        <v>18.53084018876264</v>
       </c>
       <c r="Q10">
-        <v>0.01269590831532429</v>
+        <v>0.01401974105281306</v>
       </c>
       <c r="R10">
-        <v>48.6293455730865</v>
+        <v>48.5083522950853</v>
       </c>
     </row>
     <row r="11" spans="1:18">
@@ -2491,55 +2920,55 @@
         <v>1</v>
       </c>
       <c r="B11" t="s">
-        <v>133</v>
+        <v>165</v>
       </c>
       <c r="C11" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="D11" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="E11" t="s">
-        <v>188</v>
+        <v>146</v>
       </c>
       <c r="F11">
-        <v>37.72796969950208</v>
+        <v>37.86115407109961</v>
       </c>
       <c r="G11">
         <v>650</v>
       </c>
       <c r="H11" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="I11">
         <v>9.525</v>
       </c>
       <c r="J11" t="s">
-        <v>84</v>
+        <v>104</v>
       </c>
       <c r="K11">
         <v>8.758481331682836</v>
       </c>
       <c r="L11">
-        <v>4.333333333333329</v>
+        <v>16.16666666666667</v>
       </c>
       <c r="M11">
-        <v>2.692607666666664</v>
+        <v>10.04549783333334</v>
       </c>
       <c r="N11">
-        <v>8758481.331682835</v>
+        <v>7796881.49500763</v>
       </c>
       <c r="O11">
-        <v>8694343.429134982</v>
+        <v>7527718.111210931</v>
       </c>
       <c r="P11">
-        <v>16.7590856972009</v>
+        <v>19.15178686256461</v>
       </c>
       <c r="Q11">
-        <v>0.01256218654299379</v>
+        <v>0.0145066849279918</v>
       </c>
       <c r="R11">
-        <v>46.35026176212162</v>
+        <v>49.31438456736807</v>
       </c>
     </row>
     <row r="12" spans="1:18">
@@ -2547,55 +2976,55 @@
         <v>1</v>
       </c>
       <c r="B12" t="s">
-        <v>134</v>
+        <v>167</v>
       </c>
       <c r="C12" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="D12" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="E12" t="s">
-        <v>188</v>
+        <v>146</v>
       </c>
       <c r="F12">
-        <v>37.72796969963471</v>
+        <v>37.86115407184183</v>
       </c>
       <c r="G12">
         <v>650</v>
       </c>
       <c r="H12" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="I12">
         <v>9.525</v>
       </c>
       <c r="J12" t="s">
-        <v>84</v>
+        <v>104</v>
       </c>
       <c r="K12">
         <v>8.758481331682836</v>
       </c>
       <c r="L12">
-        <v>16.16666666666667</v>
+        <v>1.166666666666657</v>
       </c>
       <c r="M12">
-        <v>10.04549783333334</v>
+        <v>0.7249328333333274</v>
       </c>
       <c r="N12">
-        <v>8694343.429134982</v>
+        <v>7527718.111210931</v>
       </c>
       <c r="O12">
-        <v>8451002.282679021</v>
+        <v>7507944.267674557</v>
       </c>
       <c r="P12">
-        <v>16.77439734614498</v>
+        <v>19.19907496065223</v>
       </c>
       <c r="Q12">
-        <v>0.01258423208641545</v>
+        <v>0.01454380190593971</v>
       </c>
       <c r="R12">
-        <v>46.97727159327673</v>
+        <v>49.37522864785075</v>
       </c>
     </row>
     <row r="13" spans="1:18">
@@ -2603,55 +3032,55 @@
         <v>1</v>
       </c>
       <c r="B13" t="s">
-        <v>135</v>
+        <v>169</v>
       </c>
       <c r="C13" t="s">
-        <v>163</v>
+        <v>170</v>
       </c>
       <c r="D13" t="s">
-        <v>164</v>
+        <v>171</v>
       </c>
       <c r="E13" t="s">
-        <v>188</v>
+        <v>146</v>
       </c>
       <c r="F13">
-        <v>37.72796969986837</v>
+        <v>37.67559114093761</v>
       </c>
       <c r="G13">
         <v>650</v>
       </c>
       <c r="H13" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="I13">
         <v>9.525</v>
       </c>
       <c r="J13" t="s">
-        <v>84</v>
+        <v>104</v>
       </c>
       <c r="K13">
         <v>8.758481331682836</v>
       </c>
       <c r="L13">
-        <v>16.16666666666667</v>
+        <v>15.00000000000001</v>
       </c>
       <c r="M13">
-        <v>10.04549783333334</v>
+        <v>9.320565000000007</v>
       </c>
       <c r="N13">
-        <v>8451002.282679021</v>
+        <v>8758481.331682835</v>
       </c>
       <c r="O13">
-        <v>8200841.267358846</v>
+        <v>8537611.996637678</v>
       </c>
       <c r="P13">
-        <v>16.78975188765184</v>
+        <v>16.93796705738677</v>
       </c>
       <c r="Q13">
-        <v>0.01260689368758529</v>
+        <v>0.01277425058001161</v>
       </c>
       <c r="R13">
-        <v>47.65039032462247</v>
+        <v>46.49074395222243</v>
       </c>
     </row>
     <row r="14" spans="1:18">
@@ -2659,55 +3088,55 @@
         <v>1</v>
       </c>
       <c r="B14" t="s">
-        <v>136</v>
+        <v>172</v>
       </c>
       <c r="C14" t="s">
-        <v>164</v>
+        <v>171</v>
       </c>
       <c r="D14" t="s">
-        <v>183</v>
+        <v>173</v>
       </c>
       <c r="E14" t="s">
-        <v>188</v>
+        <v>146</v>
       </c>
       <c r="F14">
-        <v>37.72796970000722</v>
+        <v>37.67559114095906</v>
       </c>
       <c r="G14">
         <v>650</v>
       </c>
       <c r="H14" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="I14">
         <v>9.525</v>
       </c>
       <c r="J14" t="s">
-        <v>84</v>
+        <v>104</v>
       </c>
       <c r="K14">
         <v>8.758481331682836</v>
       </c>
       <c r="L14">
-        <v>6.666666666666671</v>
+        <v>16.66666666666667</v>
       </c>
       <c r="M14">
-        <v>4.142473333333336</v>
+        <v>10.35618333333334</v>
       </c>
       <c r="N14">
-        <v>8200841.267358846</v>
+        <v>8537611.996637678</v>
       </c>
       <c r="O14">
-        <v>8095549.545282159</v>
+        <v>8285760.165049583</v>
       </c>
       <c r="P14">
-        <v>16.79609619544853</v>
+        <v>17.41874180351027</v>
       </c>
       <c r="Q14">
-        <v>0.01261623068486478</v>
+        <v>0.01315082518238736</v>
       </c>
       <c r="R14">
-        <v>47.94365329066171</v>
+        <v>47.1459340985538</v>
       </c>
     </row>
     <row r="15" spans="1:18">
@@ -2715,55 +3144,55 @@
         <v>1</v>
       </c>
       <c r="B15" t="s">
-        <v>137</v>
+        <v>174</v>
       </c>
       <c r="C15" t="s">
-        <v>165</v>
+        <v>173</v>
       </c>
       <c r="D15" t="s">
-        <v>166</v>
+        <v>175</v>
       </c>
       <c r="E15" t="s">
-        <v>188</v>
+        <v>146</v>
       </c>
       <c r="F15">
-        <v>37.63225310124334</v>
+        <v>37.67559114098225</v>
       </c>
       <c r="G15">
         <v>650</v>
       </c>
       <c r="H15" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="I15">
         <v>9.525</v>
       </c>
       <c r="J15" t="s">
-        <v>84</v>
+        <v>104</v>
       </c>
       <c r="K15">
         <v>8.758481331682836</v>
       </c>
       <c r="L15">
-        <v>10</v>
+        <v>16.66666666666667</v>
       </c>
       <c r="M15">
-        <v>6.21371</v>
+        <v>10.35618333333334</v>
       </c>
       <c r="N15">
-        <v>8758481.331682835</v>
+        <v>8285760.165049583</v>
       </c>
       <c r="O15">
-        <v>8610527.528050417</v>
+        <v>8026534.817134173</v>
       </c>
       <c r="P15">
-        <v>16.7379930373582</v>
+        <v>17.9451328313057</v>
       </c>
       <c r="Q15">
-        <v>0.01254999822767814</v>
+        <v>0.01356312459337972</v>
       </c>
       <c r="R15">
-        <v>46.56319195670006</v>
+        <v>47.85300252094136</v>
       </c>
     </row>
     <row r="16" spans="1:18">
@@ -2771,31 +3200,31 @@
         <v>1</v>
       </c>
       <c r="B16" t="s">
-        <v>138</v>
+        <v>176</v>
       </c>
       <c r="C16" t="s">
-        <v>166</v>
+        <v>175</v>
       </c>
       <c r="D16" t="s">
-        <v>167</v>
+        <v>177</v>
       </c>
       <c r="E16" t="s">
-        <v>188</v>
+        <v>146</v>
       </c>
       <c r="F16">
-        <v>37.63225310124555</v>
+        <v>37.67559114101054</v>
       </c>
       <c r="G16">
         <v>650</v>
       </c>
       <c r="H16" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="I16">
         <v>9.525</v>
       </c>
       <c r="J16" t="s">
-        <v>84</v>
+        <v>104</v>
       </c>
       <c r="K16">
         <v>8.758481331682836</v>
@@ -2807,51 +3236,51 @@
         <v>10.35618333333334</v>
       </c>
       <c r="N16">
-        <v>8610527.528050417</v>
+        <v>8026534.817134173</v>
       </c>
       <c r="O16">
-        <v>8358436.111260964</v>
+        <v>7759221.224627711</v>
       </c>
       <c r="P16">
-        <v>16.7538007793998</v>
+        <v>18.52405061120716</v>
       </c>
       <c r="Q16">
-        <v>0.01257291275165357</v>
+        <v>0.01401686360690062</v>
       </c>
       <c r="R16">
-        <v>47.22266970878732</v>
+        <v>48.61875498917193</v>
       </c>
     </row>
     <row r="17" spans="1:18">
       <c r="A17">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B17" t="s">
-        <v>139</v>
+        <v>178</v>
       </c>
       <c r="C17" t="s">
-        <v>167</v>
+        <v>179</v>
       </c>
       <c r="D17" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="E17" t="s">
-        <v>188</v>
+        <v>146</v>
       </c>
       <c r="F17">
-        <v>37.63225310124767</v>
+        <v>37.53075313710209</v>
       </c>
       <c r="G17">
         <v>650</v>
       </c>
       <c r="H17" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="I17">
         <v>9.525</v>
       </c>
       <c r="J17" t="s">
-        <v>84</v>
+        <v>104</v>
       </c>
       <c r="K17">
         <v>8.758481331682836</v>
@@ -2863,19 +3292,19 @@
         <v>10.35618333333334</v>
       </c>
       <c r="N17">
-        <v>8358436.111260964</v>
+        <v>8758481.331682835</v>
       </c>
       <c r="O17">
-        <v>8098933.185954942</v>
+        <v>8514593.452201357</v>
       </c>
       <c r="P17">
-        <v>16.76965430005646</v>
+        <v>16.91552365912592</v>
       </c>
       <c r="Q17">
-        <v>0.01259622067831441</v>
+        <v>0.01275853524433098</v>
       </c>
       <c r="R17">
-        <v>47.9341446802885</v>
+        <v>46.54949515233608</v>
       </c>
     </row>
     <row r="18" spans="1:18">
@@ -2883,31 +3312,31 @@
         <v>2</v>
       </c>
       <c r="B18" t="s">
-        <v>140</v>
+        <v>181</v>
       </c>
       <c r="C18" t="s">
-        <v>168</v>
+        <v>180</v>
       </c>
       <c r="D18" t="s">
-        <v>169</v>
+        <v>182</v>
       </c>
       <c r="E18" t="s">
-        <v>188</v>
+        <v>146</v>
       </c>
       <c r="F18">
-        <v>37.53728762671928</v>
+        <v>37.53075313710224</v>
       </c>
       <c r="G18">
         <v>650</v>
       </c>
       <c r="H18" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="I18">
         <v>9.525</v>
       </c>
       <c r="J18" t="s">
-        <v>84</v>
+        <v>104</v>
       </c>
       <c r="K18">
         <v>8.758481331682836</v>
@@ -2919,19 +3348,19 @@
         <v>10.35618333333334</v>
       </c>
       <c r="N18">
-        <v>8758481.331682835</v>
+        <v>8514593.452201357</v>
       </c>
       <c r="O18">
-        <v>8511767.951245224</v>
+        <v>8263991.053914736</v>
       </c>
       <c r="P18">
-        <v>16.72100496245979</v>
+        <v>17.39445443497452</v>
       </c>
       <c r="Q18">
-        <v>0.01254151433508201</v>
+        <v>0.01313373197375668</v>
       </c>
       <c r="R18">
-        <v>46.81824311018517</v>
+        <v>47.20387566510325</v>
       </c>
     </row>
     <row r="19" spans="1:18">
@@ -2939,31 +3368,31 @@
         <v>2</v>
       </c>
       <c r="B19" t="s">
-        <v>141</v>
+        <v>183</v>
       </c>
       <c r="C19" t="s">
-        <v>169</v>
+        <v>182</v>
       </c>
       <c r="D19" t="s">
-        <v>170</v>
+        <v>184</v>
       </c>
       <c r="E19" t="s">
-        <v>188</v>
+        <v>146</v>
       </c>
       <c r="F19">
-        <v>37.53728762671933</v>
+        <v>37.5307531371026</v>
       </c>
       <c r="G19">
         <v>650</v>
       </c>
       <c r="H19" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="I19">
         <v>9.525</v>
       </c>
       <c r="J19" t="s">
-        <v>84</v>
+        <v>104</v>
       </c>
       <c r="K19">
         <v>8.758481331682836</v>
@@ -2975,19 +3404,19 @@
         <v>10.35618333333334</v>
       </c>
       <c r="N19">
-        <v>8511767.951245224</v>
+        <v>8263991.053914736</v>
       </c>
       <c r="O19">
-        <v>8258090.346821302</v>
+        <v>8006067.616900754</v>
       </c>
       <c r="P19">
-        <v>16.73684598116004</v>
+        <v>17.91893248339389</v>
       </c>
       <c r="Q19">
-        <v>0.01256473518568816</v>
+        <v>0.01354452080968108</v>
       </c>
       <c r="R19">
-        <v>47.49317925208175</v>
+        <v>47.91023690341368</v>
       </c>
     </row>
     <row r="20" spans="1:18">
@@ -2995,31 +3424,31 @@
         <v>2</v>
       </c>
       <c r="B20" t="s">
-        <v>142</v>
+        <v>185</v>
       </c>
       <c r="C20" t="s">
-        <v>170</v>
+        <v>186</v>
       </c>
       <c r="D20" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="E20" t="s">
-        <v>188</v>
+        <v>146</v>
       </c>
       <c r="F20">
-        <v>37.53728762671938</v>
+        <v>37.4240214478632</v>
       </c>
       <c r="G20">
         <v>650</v>
       </c>
       <c r="H20" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="I20">
         <v>9.525</v>
       </c>
       <c r="J20" t="s">
-        <v>84</v>
+        <v>104</v>
       </c>
       <c r="K20">
         <v>8.758481331682836</v>
@@ -3031,19 +3460,19 @@
         <v>10.35618333333334</v>
       </c>
       <c r="N20">
-        <v>8258090.346821302</v>
+        <v>8758481.331682835</v>
       </c>
       <c r="O20">
-        <v>7996800.785368308</v>
+        <v>8515953.584780576</v>
       </c>
       <c r="P20">
-        <v>16.75273301986336</v>
+        <v>16.86489827292942</v>
       </c>
       <c r="Q20">
-        <v>0.01258803668679293</v>
+        <v>0.01272027953645654</v>
       </c>
       <c r="R20">
-        <v>48.22367103659762</v>
+        <v>46.54601743514473</v>
       </c>
     </row>
     <row r="21" spans="1:18">
@@ -3051,55 +3480,55 @@
         <v>2</v>
       </c>
       <c r="B21" t="s">
-        <v>143</v>
+        <v>188</v>
       </c>
       <c r="C21" t="s">
-        <v>171</v>
+        <v>187</v>
       </c>
       <c r="D21" t="s">
-        <v>172</v>
+        <v>189</v>
       </c>
       <c r="E21" t="s">
-        <v>188</v>
+        <v>146</v>
       </c>
       <c r="F21">
-        <v>37.42726410889182</v>
+        <v>37.42402144786337</v>
       </c>
       <c r="G21">
         <v>650</v>
       </c>
       <c r="H21" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="I21">
         <v>9.525</v>
       </c>
       <c r="J21" t="s">
-        <v>84</v>
+        <v>104</v>
       </c>
       <c r="K21">
         <v>8.758481331682836</v>
       </c>
       <c r="L21">
-        <v>16.66666666666666</v>
+        <v>16.66666666666667</v>
       </c>
       <c r="M21">
-        <v>10.35618333333333</v>
+        <v>10.35618333333334</v>
       </c>
       <c r="N21">
-        <v>8758481.331682835</v>
+        <v>8515953.584780576</v>
       </c>
       <c r="O21">
-        <v>8513186.508462738</v>
+        <v>8266788.178055216</v>
       </c>
       <c r="P21">
-        <v>16.67199492726853</v>
+        <v>17.33950766031181</v>
       </c>
       <c r="Q21">
-        <v>0.01250469302123701</v>
+        <v>0.01309208467652689</v>
       </c>
       <c r="R21">
-        <v>46.81454990266362</v>
+        <v>47.19641876096726</v>
       </c>
     </row>
     <row r="22" spans="1:18">
@@ -3107,31 +3536,31 @@
         <v>2</v>
       </c>
       <c r="B22" t="s">
-        <v>144</v>
+        <v>190</v>
       </c>
       <c r="C22" t="s">
-        <v>172</v>
+        <v>189</v>
       </c>
       <c r="D22" t="s">
-        <v>173</v>
+        <v>191</v>
       </c>
       <c r="E22" t="s">
-        <v>188</v>
+        <v>146</v>
       </c>
       <c r="F22">
-        <v>37.4272641088918</v>
+        <v>37.42402144786325</v>
       </c>
       <c r="G22">
         <v>650</v>
       </c>
       <c r="H22" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="I22">
         <v>9.525</v>
       </c>
       <c r="J22" t="s">
-        <v>84</v>
+        <v>104</v>
       </c>
       <c r="K22">
         <v>8.758481331682836</v>
@@ -3143,51 +3572,51 @@
         <v>10.35618333333334</v>
       </c>
       <c r="N22">
-        <v>8513186.508462738</v>
+        <v>8266788.178055216</v>
       </c>
       <c r="O22">
-        <v>8261009.584684702</v>
+        <v>8010389.473923942</v>
       </c>
       <c r="P22">
-        <v>16.68778951521371</v>
+        <v>17.85894758906839</v>
       </c>
       <c r="Q22">
-        <v>0.01252778448668424</v>
+        <v>0.01349892683215727</v>
       </c>
       <c r="R22">
-        <v>47.48520440303102</v>
+        <v>47.89813417917642</v>
       </c>
     </row>
     <row r="23" spans="1:18">
       <c r="A23">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B23" t="s">
-        <v>145</v>
+        <v>192</v>
       </c>
       <c r="C23" t="s">
-        <v>173</v>
+        <v>193</v>
       </c>
       <c r="D23" t="s">
-        <v>186</v>
+        <v>194</v>
       </c>
       <c r="E23" t="s">
-        <v>188</v>
+        <v>146</v>
       </c>
       <c r="F23">
-        <v>37.42726410889183</v>
+        <v>37.31823697282097</v>
       </c>
       <c r="G23">
         <v>650</v>
       </c>
       <c r="H23" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="I23">
         <v>9.525</v>
       </c>
       <c r="J23" t="s">
-        <v>84</v>
+        <v>104</v>
       </c>
       <c r="K23">
         <v>8.758481331682836</v>
@@ -3199,19 +3628,19 @@
         <v>10.35618333333334</v>
       </c>
       <c r="N23">
-        <v>8261009.584684702</v>
+        <v>8758481.331682835</v>
       </c>
       <c r="O23">
-        <v>8001314.936959958</v>
+        <v>8517297.79034972</v>
       </c>
       <c r="P23">
-        <v>16.70362998827537</v>
+        <v>16.81474422030363</v>
       </c>
       <c r="Q23">
-        <v>0.01255093887932279</v>
+        <v>0.0126823806123424</v>
       </c>
       <c r="R23">
-        <v>48.21076326695984</v>
+        <v>46.54258120736829</v>
       </c>
     </row>
     <row r="24" spans="1:18">
@@ -3219,31 +3648,31 @@
         <v>3</v>
       </c>
       <c r="B24" t="s">
+        <v>195</v>
+      </c>
+      <c r="C24" t="s">
+        <v>194</v>
+      </c>
+      <c r="D24" t="s">
+        <v>196</v>
+      </c>
+      <c r="E24" t="s">
         <v>146</v>
       </c>
-      <c r="C24" t="s">
-        <v>174</v>
-      </c>
-      <c r="D24" t="s">
-        <v>175</v>
-      </c>
-      <c r="E24" t="s">
-        <v>188</v>
-      </c>
       <c r="F24">
-        <v>37.31823697282104</v>
+        <v>37.31823697282101</v>
       </c>
       <c r="G24">
         <v>650</v>
       </c>
       <c r="H24" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="I24">
         <v>9.525</v>
       </c>
       <c r="J24" t="s">
-        <v>84</v>
+        <v>104</v>
       </c>
       <c r="K24">
         <v>8.758481331682836</v>
@@ -3255,19 +3684,19 @@
         <v>10.35618333333334</v>
       </c>
       <c r="N24">
-        <v>8758481.331682835</v>
+        <v>8517297.79034972</v>
       </c>
       <c r="O24">
-        <v>8514588.068679847</v>
+        <v>8269552.089659391</v>
       </c>
       <c r="P24">
-        <v>16.6234287308664</v>
+        <v>17.28509914109673</v>
       </c>
       <c r="Q24">
-        <v>0.01246820571919365</v>
+        <v>0.01305084677696233</v>
       </c>
       <c r="R24">
-        <v>46.81090180498303</v>
+        <v>47.18905386890999</v>
       </c>
     </row>
     <row r="25" spans="1:18">
@@ -3275,31 +3704,31 @@
         <v>3</v>
       </c>
       <c r="B25" t="s">
-        <v>147</v>
+        <v>197</v>
       </c>
       <c r="C25" t="s">
-        <v>175</v>
+        <v>196</v>
       </c>
       <c r="D25" t="s">
-        <v>176</v>
+        <v>198</v>
       </c>
       <c r="E25" t="s">
-        <v>188</v>
+        <v>146</v>
       </c>
       <c r="F25">
-        <v>37.31823697282097</v>
+        <v>37.31823697282103</v>
       </c>
       <c r="G25">
         <v>650</v>
       </c>
       <c r="H25" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="I25">
         <v>9.525</v>
       </c>
       <c r="J25" t="s">
-        <v>84</v>
+        <v>104</v>
       </c>
       <c r="K25">
         <v>8.758481331682836</v>
@@ -3311,19 +3740,19 @@
         <v>10.35618333333334</v>
       </c>
       <c r="N25">
-        <v>8514588.068679847</v>
+        <v>8269552.089659391</v>
       </c>
       <c r="O25">
-        <v>8263893.339292537</v>
+        <v>8014659.214613608</v>
       </c>
       <c r="P25">
-        <v>16.63917730853723</v>
+        <v>17.79958342949392</v>
       </c>
       <c r="Q25">
-        <v>0.01249116958626076</v>
+        <v>0.01345380701381957</v>
       </c>
       <c r="R25">
-        <v>47.47733043109715</v>
+        <v>47.88618640121708</v>
       </c>
     </row>
     <row r="26" spans="1:18">
@@ -3331,16 +3760,16 @@
         <v>3</v>
       </c>
       <c r="B26" t="s">
-        <v>148</v>
+        <v>199</v>
       </c>
       <c r="C26" t="s">
-        <v>176</v>
+        <v>198</v>
       </c>
       <c r="D26" t="s">
-        <v>177</v>
+        <v>200</v>
       </c>
       <c r="E26" t="s">
-        <v>188</v>
+        <v>146</v>
       </c>
       <c r="F26">
         <v>37.318236972821</v>
@@ -3349,13 +3778,13 @@
         <v>650</v>
       </c>
       <c r="H26" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="I26">
         <v>9.525</v>
       </c>
       <c r="J26" t="s">
-        <v>84</v>
+        <v>104</v>
       </c>
       <c r="K26">
         <v>8.758481331682836</v>
@@ -3367,19 +3796,19 @@
         <v>10.35618333333334</v>
       </c>
       <c r="N26">
-        <v>8263893.339292537</v>
+        <v>8014659.214613608</v>
       </c>
       <c r="O26">
-        <v>8005773.332778163</v>
+        <v>7751939.218135473</v>
       </c>
       <c r="P26">
-        <v>16.65497163765936</v>
+        <v>18.36453149602891</v>
       </c>
       <c r="Q26">
-        <v>0.0125141790690114</v>
+        <v>0.01389659331803264</v>
       </c>
       <c r="R26">
-        <v>48.19802509366989</v>
+        <v>48.64018960350258</v>
       </c>
     </row>
     <row r="27" spans="1:18">
@@ -3387,31 +3816,31 @@
         <v>3</v>
       </c>
       <c r="B27" t="s">
-        <v>149</v>
+        <v>201</v>
       </c>
       <c r="C27" t="s">
-        <v>177</v>
+        <v>200</v>
       </c>
       <c r="D27" t="s">
-        <v>178</v>
+        <v>202</v>
       </c>
       <c r="E27" t="s">
-        <v>188</v>
+        <v>146</v>
       </c>
       <c r="F27">
-        <v>37.31823697282101</v>
+        <v>37.31823697282107</v>
       </c>
       <c r="G27">
         <v>650</v>
       </c>
       <c r="H27" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="I27">
         <v>9.525</v>
       </c>
       <c r="J27" t="s">
-        <v>84</v>
+        <v>104</v>
       </c>
       <c r="K27">
         <v>8.758481331682836</v>
@@ -3423,19 +3852,19 @@
         <v>10.35618333333334</v>
       </c>
       <c r="N27">
-        <v>8005773.332778163</v>
+        <v>7751939.218135473</v>
       </c>
       <c r="O27">
-        <v>7739504.085621269</v>
+        <v>7480581.274476196</v>
       </c>
       <c r="P27">
-        <v>16.67081194198452</v>
+        <v>18.98892150746561</v>
       </c>
       <c r="Q27">
-        <v>0.01253783275548484</v>
+        <v>0.01438629062639513</v>
       </c>
       <c r="R27">
-        <v>48.97883457136526</v>
+        <v>49.46015603710492</v>
       </c>
     </row>
     <row r="28" spans="1:18">
@@ -3443,31 +3872,31 @@
         <v>3</v>
       </c>
       <c r="B28" t="s">
-        <v>150</v>
+        <v>203</v>
       </c>
       <c r="C28" t="s">
-        <v>178</v>
+        <v>202</v>
       </c>
       <c r="D28" t="s">
-        <v>179</v>
+        <v>204</v>
       </c>
       <c r="E28" t="s">
-        <v>188</v>
+        <v>146</v>
       </c>
       <c r="F28">
-        <v>37.31823697282106</v>
+        <v>37.31823697282095</v>
       </c>
       <c r="G28">
         <v>650</v>
       </c>
       <c r="H28" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="I28">
         <v>9.525</v>
       </c>
       <c r="J28" t="s">
-        <v>84</v>
+        <v>104</v>
       </c>
       <c r="K28">
         <v>8.758481331682836</v>
@@ -3479,75 +3908,19 @@
         <v>10.35618333333334</v>
       </c>
       <c r="N28">
-        <v>7739504.085621269</v>
+        <v>7480581.274476196</v>
       </c>
       <c r="O28">
-        <v>7464214.197561333</v>
+        <v>7199642.134692008</v>
       </c>
       <c r="P28">
-        <v>16.68669844680667</v>
+        <v>19.68478044912923</v>
       </c>
       <c r="Q28">
-        <v>0.01256209459644473</v>
+        <v>0.01493211603992332</v>
       </c>
       <c r="R28">
-        <v>49.82996189517983</v>
-      </c>
-    </row>
-    <row r="29" spans="1:18">
-      <c r="A29">
-        <v>3</v>
-      </c>
-      <c r="B29" t="s">
-        <v>151</v>
-      </c>
-      <c r="C29" t="s">
-        <v>179</v>
-      </c>
-      <c r="D29" t="s">
-        <v>187</v>
-      </c>
-      <c r="E29" t="s">
-        <v>188</v>
-      </c>
-      <c r="F29">
-        <v>37.31823697282098</v>
-      </c>
-      <c r="G29">
-        <v>650</v>
-      </c>
-      <c r="H29" t="s">
-        <v>85</v>
-      </c>
-      <c r="I29">
-        <v>9.525</v>
-      </c>
-      <c r="J29" t="s">
-        <v>84</v>
-      </c>
-      <c r="K29">
-        <v>8.758481331682836</v>
-      </c>
-      <c r="L29">
-        <v>16.66666666666667</v>
-      </c>
-      <c r="M29">
-        <v>10.35618333333334</v>
-      </c>
-      <c r="N29">
-        <v>7464214.197561333</v>
-      </c>
-      <c r="O29">
-        <v>7178890.867953929</v>
-      </c>
-      <c r="P29">
-        <v>16.70263137897549</v>
-      </c>
-      <c r="Q29">
-        <v>0.01258658396492461</v>
-      </c>
-      <c r="R29">
-        <v>50.76547770199675</v>
+        <v>50.3582489131251</v>
       </c>
     </row>
   </sheetData>
@@ -3557,63 +3930,63 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R8"/>
+  <dimension ref="A1:R7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:18">
-      <c r="A1" s="2" t="s">
-        <v>189</v>
-      </c>
-      <c r="B1" s="2" t="s">
+      <c r="A1" t="s">
+        <v>205</v>
+      </c>
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>190</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>191</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>192</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>193</v>
-      </c>
-      <c r="J1" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="K1" s="2" t="s">
-        <v>194</v>
-      </c>
-      <c r="L1" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="M1" s="2" t="s">
-        <v>195</v>
-      </c>
-      <c r="N1" s="2" t="s">
-        <v>196</v>
-      </c>
-      <c r="O1" s="2" t="s">
-        <v>197</v>
-      </c>
-      <c r="P1" s="2" t="s">
-        <v>198</v>
-      </c>
-      <c r="Q1" s="2" t="s">
-        <v>199</v>
-      </c>
-      <c r="R1" s="2" t="s">
-        <v>200</v>
+      <c r="C1" t="s">
+        <v>129</v>
+      </c>
+      <c r="D1" t="s">
+        <v>130</v>
+      </c>
+      <c r="E1" t="s">
+        <v>131</v>
+      </c>
+      <c r="F1" t="s">
+        <v>206</v>
+      </c>
+      <c r="G1" t="s">
+        <v>207</v>
+      </c>
+      <c r="H1" t="s">
+        <v>208</v>
+      </c>
+      <c r="I1" t="s">
+        <v>209</v>
+      </c>
+      <c r="J1" t="s">
+        <v>114</v>
+      </c>
+      <c r="K1" t="s">
+        <v>210</v>
+      </c>
+      <c r="L1" t="s">
+        <v>120</v>
+      </c>
+      <c r="M1" t="s">
+        <v>211</v>
+      </c>
+      <c r="N1" t="s">
+        <v>212</v>
+      </c>
+      <c r="O1" t="s">
+        <v>213</v>
+      </c>
+      <c r="P1" t="s">
+        <v>214</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>215</v>
+      </c>
+      <c r="R1" t="s">
+        <v>216</v>
       </c>
     </row>
     <row r="2" spans="1:18">
@@ -3621,16 +3994,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>101</v>
+        <v>121</v>
       </c>
       <c r="C2" t="s">
-        <v>180</v>
+        <v>150</v>
       </c>
       <c r="D2" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="E2" t="s">
-        <v>201</v>
+        <v>217</v>
       </c>
       <c r="F2">
         <v>35</v>
@@ -3639,22 +4012,22 @@
         <v>21.747985</v>
       </c>
       <c r="H2">
-        <v>1.10975212252264</v>
+        <v>1.108359633917611</v>
       </c>
       <c r="I2">
-        <v>74.95491554868013</v>
+        <v>72.98929459785241</v>
       </c>
       <c r="J2">
-        <v>7.842291708880055</v>
+        <v>7.63663511154234</v>
       </c>
       <c r="K2">
-        <v>10516.67002744233</v>
+        <v>10240.88041728051</v>
       </c>
       <c r="L2">
         <v>0</v>
       </c>
       <c r="M2">
-        <v>7.842291708880055</v>
+        <v>7.63663511154234</v>
       </c>
       <c r="N2">
         <v>0.78</v>
@@ -3663,27 +4036,27 @@
         <v>0.357</v>
       </c>
       <c r="P2">
-        <v>18311088.15709077</v>
+        <v>17995750.75756607</v>
       </c>
       <c r="Q2">
         <v>0</v>
       </c>
       <c r="R2">
-        <v>18311088.15709077</v>
+        <v>17995750.75756607</v>
       </c>
     </row>
     <row r="3" spans="1:18">
       <c r="B3" t="s">
-        <v>102</v>
+        <v>122</v>
       </c>
       <c r="C3" t="s">
-        <v>181</v>
+        <v>157</v>
       </c>
       <c r="D3" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E3" t="s">
-        <v>188</v>
+        <v>146</v>
       </c>
       <c r="F3">
         <v>70</v>
@@ -3692,16 +4065,16 @@
         <v>43.49597</v>
       </c>
       <c r="H3">
-        <v>1.10005905191529</v>
+        <v>1.098739771845158</v>
       </c>
       <c r="I3">
-        <v>68.51788452321429</v>
+        <v>66.54382841245881</v>
       </c>
       <c r="J3">
-        <v>7.168805858468696</v>
+        <v>6.96226671748084</v>
       </c>
       <c r="K3">
-        <v>9613.51203232369</v>
+        <v>9336.538913476155</v>
       </c>
       <c r="L3">
         <v>0</v>
@@ -3730,40 +4103,40 @@
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>103</v>
+        <v>123</v>
       </c>
       <c r="C4" t="s">
-        <v>182</v>
+        <v>168</v>
       </c>
       <c r="D4" t="s">
-        <v>161</v>
+        <v>170</v>
       </c>
       <c r="E4" t="s">
-        <v>201</v>
+        <v>217</v>
       </c>
       <c r="F4">
-        <v>113.3333333333333</v>
+        <v>135</v>
       </c>
       <c r="G4">
-        <v>70.42204666666667</v>
+        <v>83.885085</v>
       </c>
       <c r="H4">
-        <v>1.114771055406689</v>
+        <v>1.166561846948234</v>
       </c>
       <c r="I4">
-        <v>63.92631159315608</v>
+        <v>89.79407618045634</v>
       </c>
       <c r="J4">
-        <v>6.688404352356296</v>
+        <v>9.394865353149434</v>
       </c>
       <c r="K4">
-        <v>8969.284004596841</v>
+        <v>12598.70233588045</v>
       </c>
       <c r="L4">
         <v>0</v>
       </c>
       <c r="M4">
-        <v>6.688404352356296</v>
+        <v>9.394865353149434</v>
       </c>
       <c r="N4">
         <v>0.78</v>
@@ -3772,54 +4145,51 @@
         <v>0.357</v>
       </c>
       <c r="P4">
-        <v>16550382.92341388</v>
+        <v>20713070.39647818</v>
       </c>
       <c r="Q4">
         <v>0</v>
       </c>
       <c r="R4">
-        <v>16550382.92341388</v>
+        <v>20713070.39647818</v>
       </c>
     </row>
     <row r="5" spans="1:18">
-      <c r="A5">
-        <v>1</v>
-      </c>
       <c r="B5" t="s">
-        <v>104</v>
+        <v>124</v>
       </c>
       <c r="C5" t="s">
-        <v>183</v>
+        <v>177</v>
       </c>
       <c r="D5" t="s">
-        <v>165</v>
+        <v>179</v>
       </c>
       <c r="E5" t="s">
-        <v>201</v>
+        <v>146</v>
       </c>
       <c r="F5">
-        <v>156.6666666666667</v>
+        <v>200</v>
       </c>
       <c r="G5">
-        <v>97.34812333333335</v>
+        <v>124.2742</v>
       </c>
       <c r="H5">
-        <v>1.081888423101186</v>
+        <v>1.128783556767718</v>
       </c>
       <c r="I5">
-        <v>46.31734515285845</v>
+        <v>70.0872320210356</v>
       </c>
       <c r="J5">
-        <v>4.846034835883339</v>
+        <v>7.333001639097953</v>
       </c>
       <c r="K5">
-        <v>6498.629635616275</v>
+        <v>9833.701858063136</v>
       </c>
       <c r="L5">
         <v>0</v>
       </c>
       <c r="M5">
-        <v>4.846034835883339</v>
+        <v>12.5</v>
       </c>
       <c r="N5">
         <v>0.78</v>
@@ -3828,51 +4198,54 @@
         <v>0.357</v>
       </c>
       <c r="P5">
-        <v>13782384.48884103</v>
+        <v>0</v>
       </c>
       <c r="Q5">
-        <v>0</v>
+        <v>16916025.69007904</v>
       </c>
       <c r="R5">
-        <v>13782384.48884103</v>
+        <v>16916025.69007904</v>
       </c>
     </row>
     <row r="6" spans="1:18">
+      <c r="A6">
+        <v>2</v>
+      </c>
       <c r="B6" t="s">
-        <v>105</v>
+        <v>125</v>
       </c>
       <c r="C6" t="s">
         <v>184</v>
       </c>
       <c r="D6" t="s">
-        <v>168</v>
+        <v>186</v>
       </c>
       <c r="E6" t="s">
-        <v>188</v>
+        <v>217</v>
       </c>
       <c r="F6">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="G6">
-        <v>124.2742</v>
+        <v>155.34275</v>
       </c>
       <c r="H6">
-        <v>1.081436422623127</v>
+        <v>1.093980434688528</v>
       </c>
       <c r="I6">
-        <v>45.95387296195558</v>
+        <v>51.64755413256176</v>
       </c>
       <c r="J6">
-        <v>4.808005909718052</v>
+        <v>5.403717455924144</v>
       </c>
       <c r="K6">
-        <v>6447.632085050102</v>
+        <v>7246.493182743396</v>
       </c>
       <c r="L6">
         <v>0</v>
       </c>
       <c r="M6">
-        <v>12.5</v>
+        <v>5.403717455924144</v>
       </c>
       <c r="N6">
         <v>0.78</v>
@@ -3881,54 +4254,51 @@
         <v>0.357</v>
       </c>
       <c r="P6">
+        <v>14614639.77251345</v>
+      </c>
+      <c r="Q6">
         <v>0</v>
       </c>
-      <c r="Q6">
-        <v>16916025.69007904</v>
-      </c>
       <c r="R6">
-        <v>16916025.69007904</v>
+        <v>14614639.77251345</v>
       </c>
     </row>
     <row r="7" spans="1:18">
-      <c r="A7">
-        <v>2</v>
-      </c>
       <c r="B7" t="s">
-        <v>106</v>
+        <v>126</v>
       </c>
       <c r="C7" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
       <c r="D7" t="s">
-        <v>171</v>
+        <v>193</v>
       </c>
       <c r="E7" t="s">
-        <v>201</v>
+        <v>146</v>
       </c>
       <c r="F7">
-        <v>250</v>
+        <v>300</v>
       </c>
       <c r="G7">
-        <v>155.34275</v>
+        <v>186.4113</v>
       </c>
       <c r="H7">
-        <v>1.095248158201986</v>
+        <v>1.093390197841708</v>
       </c>
       <c r="I7">
-        <v>53.24047275228795</v>
+        <v>51.18919638551989</v>
       </c>
       <c r="J7">
-        <v>5.570379407217869</v>
+        <v>5.355760959235239</v>
       </c>
       <c r="K7">
-        <v>7469.990192667306</v>
+        <v>7182.18256155364</v>
       </c>
       <c r="L7">
         <v>0</v>
       </c>
       <c r="M7">
-        <v>5.570379407217869</v>
+        <v>12.5</v>
       </c>
       <c r="N7">
         <v>0.78</v>
@@ -3937,65 +4307,12 @@
         <v>0.357</v>
       </c>
       <c r="P7">
-        <v>14864302.96021254</v>
+        <v>0</v>
       </c>
       <c r="Q7">
-        <v>0</v>
+        <v>16916025.69007904</v>
       </c>
       <c r="R7">
-        <v>14864302.96021254</v>
-      </c>
-    </row>
-    <row r="8" spans="1:18">
-      <c r="B8" t="s">
-        <v>107</v>
-      </c>
-      <c r="C8" t="s">
-        <v>186</v>
-      </c>
-      <c r="D8" t="s">
-        <v>174</v>
-      </c>
-      <c r="E8" t="s">
-        <v>188</v>
-      </c>
-      <c r="F8">
-        <v>300.0000000000001</v>
-      </c>
-      <c r="G8">
-        <v>186.4113</v>
-      </c>
-      <c r="H8">
-        <v>1.094630245239485</v>
-      </c>
-      <c r="I8">
-        <v>52.75832278267718</v>
-      </c>
-      <c r="J8">
-        <v>5.519933606813229</v>
-      </c>
-      <c r="K8">
-        <v>7402.341365408676</v>
-      </c>
-      <c r="L8">
-        <v>0</v>
-      </c>
-      <c r="M8">
-        <v>12.5</v>
-      </c>
-      <c r="N8">
-        <v>0.78</v>
-      </c>
-      <c r="O8">
-        <v>0.357</v>
-      </c>
-      <c r="P8">
-        <v>0</v>
-      </c>
-      <c r="Q8">
-        <v>16916025.69007904</v>
-      </c>
-      <c r="R8">
         <v>16916025.69007904</v>
       </c>
     </row>
@@ -4006,20 +4323,20 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B37"/>
+  <dimension ref="A1:B35"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
-      <c r="A1" s="2" t="s">
-        <v>202</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>203</v>
+      <c r="A1" t="s">
+        <v>218</v>
+      </c>
+      <c r="B1" t="s">
+        <v>219</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>152</v>
+        <v>144</v>
       </c>
       <c r="B2">
         <v>8700000</v>
@@ -4027,31 +4344,31 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="B3">
-        <v>8400980.744238859</v>
+        <v>8404437.121807171</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="B4">
-        <v>8091531.137787693</v>
+        <v>8098822.381386424</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>180</v>
+        <v>150</v>
       </c>
       <c r="B5">
-        <v>7892286.172675607</v>
+        <v>7902201.653379492</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="B6">
         <v>8758481.331682835</v>
@@ -4059,31 +4376,31 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="B7">
-        <v>8648934.335705761</v>
+        <v>8650145.275655651</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="B8">
-        <v>8312110.789706063</v>
+        <v>8317246.107158598</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>181</v>
+        <v>157</v>
       </c>
       <c r="B9">
-        <v>7961828.336791218</v>
+        <v>7971388.272378965</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B10">
         <v>8758481.331682835</v>
@@ -4091,218 +4408,202 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B11">
-        <v>8410967.683713766</v>
+        <v>8414863.001234222</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="B12">
-        <v>8049296.565045817</v>
+        <v>8057594.965673572</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" t="s">
-        <v>182</v>
+        <v>164</v>
       </c>
       <c r="B13">
-        <v>7856753.446551932</v>
+        <v>7796881.49500763</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="B14">
-        <v>8758481.331682835</v>
+        <v>7527718.111210931</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" t="s">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="B15">
-        <v>8694343.429134982</v>
+        <v>7507944.267674557</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" t="s">
-        <v>163</v>
+        <v>170</v>
       </c>
       <c r="B16">
-        <v>8451002.282679021</v>
+        <v>8758481.331682835</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" t="s">
-        <v>164</v>
+        <v>171</v>
       </c>
       <c r="B17">
-        <v>8200841.267358846</v>
+        <v>8537611.996637678</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" t="s">
-        <v>183</v>
+        <v>173</v>
       </c>
       <c r="B18">
-        <v>8095549.545282159</v>
+        <v>8285760.165049583</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" t="s">
-        <v>165</v>
+        <v>175</v>
       </c>
       <c r="B19">
-        <v>8758481.331682835</v>
+        <v>8026534.817134173</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" t="s">
-        <v>166</v>
+        <v>177</v>
       </c>
       <c r="B20">
-        <v>8610527.528050417</v>
+        <v>7759221.224627711</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" t="s">
-        <v>167</v>
+        <v>179</v>
       </c>
       <c r="B21">
-        <v>8358436.111260964</v>
+        <v>8758481.331682835</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="B22">
-        <v>8098933.185954942</v>
+        <v>8514593.452201357</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" t="s">
-        <v>168</v>
+        <v>182</v>
       </c>
       <c r="B23">
-        <v>8758481.331682835</v>
+        <v>8263991.053914736</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" t="s">
-        <v>169</v>
+        <v>186</v>
       </c>
       <c r="B24">
-        <v>8511767.951245224</v>
+        <v>8758481.331682835</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" t="s">
-        <v>170</v>
+        <v>184</v>
       </c>
       <c r="B25">
-        <v>8258090.346821302</v>
+        <v>8006067.616900754</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="B26">
-        <v>7996800.785368308</v>
+        <v>8515953.584780576</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" t="s">
-        <v>171</v>
+        <v>189</v>
       </c>
       <c r="B27">
-        <v>8758481.331682835</v>
+        <v>8266788.178055216</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" t="s">
-        <v>172</v>
+        <v>191</v>
       </c>
       <c r="B28">
-        <v>8513186.508462738</v>
+        <v>8010389.473923942</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" t="s">
-        <v>173</v>
+        <v>193</v>
       </c>
       <c r="B29">
-        <v>8261009.584684702</v>
+        <v>8758481.331682835</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" t="s">
-        <v>186</v>
+        <v>194</v>
       </c>
       <c r="B30">
-        <v>8001314.936959958</v>
+        <v>8517297.79034972</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" t="s">
-        <v>174</v>
+        <v>196</v>
       </c>
       <c r="B31">
-        <v>8758481.331682835</v>
+        <v>8269552.089659391</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" t="s">
-        <v>175</v>
+        <v>198</v>
       </c>
       <c r="B32">
-        <v>8514588.068679847</v>
+        <v>8014659.214613608</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" t="s">
-        <v>176</v>
+        <v>200</v>
       </c>
       <c r="B33">
-        <v>8263893.339292537</v>
+        <v>7751939.218135473</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" t="s">
-        <v>177</v>
+        <v>202</v>
       </c>
       <c r="B34">
-        <v>8005773.332778163</v>
+        <v>7480581.274476196</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" t="s">
-        <v>178</v>
+        <v>204</v>
       </c>
       <c r="B35">
-        <v>7739504.085621269</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2">
-      <c r="A36" t="s">
-        <v>179</v>
-      </c>
-      <c r="B36">
-        <v>7464214.197561333</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2">
-      <c r="A37" t="s">
-        <v>187</v>
-      </c>
-      <c r="B37">
-        <v>7178890.867953929</v>
+        <v>7199642.134692008</v>
       </c>
     </row>
   </sheetData>
@@ -4316,37 +4617,37 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" s="2" t="s">
-        <v>204</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>206</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>207</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>208</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>209</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>210</v>
+      <c r="A1" t="s">
+        <v>220</v>
+      </c>
+      <c r="B1" t="s">
+        <v>221</v>
+      </c>
+      <c r="C1" t="s">
+        <v>222</v>
+      </c>
+      <c r="D1" t="s">
+        <v>223</v>
+      </c>
+      <c r="E1" t="s">
+        <v>224</v>
+      </c>
+      <c r="F1" t="s">
+        <v>225</v>
+      </c>
+      <c r="G1" t="s">
+        <v>226</v>
       </c>
     </row>
     <row r="2" spans="1:7">
       <c r="A2" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="B2">
         <v>8.11266027279845</v>
       </c>
       <c r="C2">
-        <v>8.112660180781688</v>
+        <v>8.112660264998453</v>
       </c>
       <c r="D2">
         <v>141.8178946624533</v>
@@ -4355,21 +4656,21 @@
         <v>1150.5204</v>
       </c>
       <c r="F2">
-        <v>1150.520386950377</v>
+        <v>1150.520398893821</v>
       </c>
       <c r="G2">
-        <v>-1.134236601997908E-06</v>
+        <v>-9.614598455224869E-08</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3" t="s">
-        <v>187</v>
+        <v>204</v>
       </c>
       <c r="B3">
         <v>21.09291642722411</v>
       </c>
       <c r="C3">
-        <v>21.0929164272241</v>
+        <v>21.09291642722408</v>
       </c>
       <c r="D3">
         <v>141.8178946624533</v>
@@ -4378,21 +4679,21 @@
         <v>2991.353</v>
       </c>
       <c r="F3">
-        <v>2991.352999999998</v>
+        <v>2991.352999999995</v>
       </c>
       <c r="G3">
-        <v>-6.737264030904896E-14</v>
+        <v>-1.684316007726224E-13</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4" t="s">
-        <v>211</v>
+        <v>227</v>
       </c>
       <c r="B4">
         <v>16.2253205455969</v>
       </c>
       <c r="C4">
-        <v>16.22532054559689</v>
+        <v>16.22532054559687</v>
       </c>
       <c r="D4">
         <v>141.8178946624533</v>
@@ -4401,10 +4702,843 @@
         <v>2301.0408</v>
       </c>
       <c r="F4">
-        <v>2301.040799999999</v>
+        <v>2301.040799999996</v>
       </c>
       <c r="G4">
-        <v>-6.568832342294664E-14</v>
+        <v>-1.75168862461191E-13</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:I50"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:9">
+      <c r="A1" t="s">
+        <v>228</v>
+      </c>
+      <c r="B1" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
+      <c r="A2" t="s">
+        <v>230</v>
+      </c>
+      <c r="B2" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
+      <c r="A3" t="s">
+        <v>232</v>
+      </c>
+      <c r="B3" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
+      <c r="A4" t="s">
+        <v>234</v>
+      </c>
+      <c r="B4" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9">
+      <c r="A5" t="s">
+        <v>236</v>
+      </c>
+      <c r="B5" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
+      <c r="A6" t="s">
+        <v>238</v>
+      </c>
+      <c r="B6" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9">
+      <c r="A7" t="s">
+        <v>240</v>
+      </c>
+      <c r="B7" t="s">
+        <v>241</v>
+      </c>
+      <c r="C7" t="s">
+        <v>242</v>
+      </c>
+      <c r="D7" t="s">
+        <v>243</v>
+      </c>
+      <c r="E7" t="s">
+        <v>242</v>
+      </c>
+      <c r="F7" t="s">
+        <v>244</v>
+      </c>
+      <c r="G7" t="s">
+        <v>242</v>
+      </c>
+      <c r="H7" t="s">
+        <v>245</v>
+      </c>
+      <c r="I7" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9">
+      <c r="A8" t="s">
+        <v>246</v>
+      </c>
+      <c r="B8" t="s">
+        <v>247</v>
+      </c>
+      <c r="C8" t="s">
+        <v>248</v>
+      </c>
+      <c r="D8" t="s">
+        <v>249</v>
+      </c>
+      <c r="E8" t="s">
+        <v>250</v>
+      </c>
+      <c r="F8" t="s">
+        <v>251</v>
+      </c>
+      <c r="G8" t="s">
+        <v>252</v>
+      </c>
+      <c r="H8" t="s">
+        <v>253</v>
+      </c>
+      <c r="I8" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9">
+      <c r="A9" t="s">
+        <v>255</v>
+      </c>
+      <c r="B9" t="s">
+        <v>256</v>
+      </c>
+      <c r="C9" t="s">
+        <v>242</v>
+      </c>
+      <c r="D9" t="s">
+        <v>243</v>
+      </c>
+      <c r="E9" t="s">
+        <v>242</v>
+      </c>
+      <c r="F9" t="s">
+        <v>245</v>
+      </c>
+      <c r="G9" t="s">
+        <v>233</v>
+      </c>
+      <c r="H9" t="s">
+        <v>257</v>
+      </c>
+      <c r="I9" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9">
+      <c r="A10" t="s">
+        <v>259</v>
+      </c>
+      <c r="B10" t="s">
+        <v>256</v>
+      </c>
+      <c r="C10" t="s">
+        <v>242</v>
+      </c>
+      <c r="D10" t="s">
+        <v>253</v>
+      </c>
+      <c r="E10" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9">
+      <c r="A11" t="s">
+        <v>260</v>
+      </c>
+      <c r="B11" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9">
+      <c r="A12" t="s">
+        <v>261</v>
+      </c>
+      <c r="B12" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9">
+      <c r="A13" t="s">
+        <v>262</v>
+      </c>
+      <c r="B13" t="s">
+        <v>256</v>
+      </c>
+      <c r="C13" t="s">
+        <v>242</v>
+      </c>
+      <c r="D13" t="s">
+        <v>253</v>
+      </c>
+      <c r="E13" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9">
+      <c r="A14" t="s">
+        <v>263</v>
+      </c>
+      <c r="B14" t="s">
+        <v>256</v>
+      </c>
+      <c r="C14" t="s">
+        <v>242</v>
+      </c>
+      <c r="D14" t="s">
+        <v>264</v>
+      </c>
+      <c r="E14" t="s">
+        <v>242</v>
+      </c>
+      <c r="F14" t="s">
+        <v>253</v>
+      </c>
+      <c r="G14" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9">
+      <c r="A15" t="s">
+        <v>265</v>
+      </c>
+      <c r="B15" t="s">
+        <v>256</v>
+      </c>
+      <c r="C15" t="s">
+        <v>242</v>
+      </c>
+      <c r="D15" t="s">
+        <v>253</v>
+      </c>
+      <c r="E15" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9">
+      <c r="A16" t="s">
+        <v>266</v>
+      </c>
+      <c r="B16" t="s">
+        <v>256</v>
+      </c>
+      <c r="C16" t="s">
+        <v>242</v>
+      </c>
+      <c r="D16" t="s">
+        <v>253</v>
+      </c>
+      <c r="E16" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9">
+      <c r="A17" t="s">
+        <v>267</v>
+      </c>
+      <c r="B17" t="s">
+        <v>256</v>
+      </c>
+      <c r="C17" t="s">
+        <v>242</v>
+      </c>
+      <c r="D17" t="s">
+        <v>253</v>
+      </c>
+      <c r="E17" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9">
+      <c r="A18" t="s">
+        <v>268</v>
+      </c>
+      <c r="B18" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9">
+      <c r="A19" t="s">
+        <v>269</v>
+      </c>
+      <c r="B19" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9">
+      <c r="A20" t="s">
+        <v>270</v>
+      </c>
+      <c r="B20" t="s">
+        <v>256</v>
+      </c>
+      <c r="C20" t="s">
+        <v>242</v>
+      </c>
+      <c r="D20" t="s">
+        <v>271</v>
+      </c>
+      <c r="E20" t="s">
+        <v>272</v>
+      </c>
+      <c r="F20" t="s">
+        <v>273</v>
+      </c>
+      <c r="G20" t="s">
+        <v>274</v>
+      </c>
+      <c r="H20" t="s">
+        <v>275</v>
+      </c>
+      <c r="I20" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9">
+      <c r="A21" t="s">
+        <v>276</v>
+      </c>
+      <c r="B21" t="s">
+        <v>256</v>
+      </c>
+      <c r="C21" t="s">
+        <v>242</v>
+      </c>
+      <c r="D21" t="s">
+        <v>271</v>
+      </c>
+      <c r="E21" t="s">
+        <v>277</v>
+      </c>
+      <c r="F21" t="s">
+        <v>273</v>
+      </c>
+      <c r="G21" t="s">
+        <v>274</v>
+      </c>
+      <c r="H21" t="s">
+        <v>275</v>
+      </c>
+      <c r="I21" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9">
+      <c r="A22" t="s">
+        <v>278</v>
+      </c>
+      <c r="B22" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9">
+      <c r="A23" t="s">
+        <v>280</v>
+      </c>
+      <c r="B23" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9">
+      <c r="A24" t="s">
+        <v>282</v>
+      </c>
+      <c r="B24" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9">
+      <c r="A25" t="s">
+        <v>283</v>
+      </c>
+      <c r="B25" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9">
+      <c r="A26" t="s">
+        <v>285</v>
+      </c>
+      <c r="B26" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9">
+      <c r="A27" t="s">
+        <v>286</v>
+      </c>
+      <c r="B27" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9">
+      <c r="A28" t="s">
+        <v>287</v>
+      </c>
+      <c r="B28" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9">
+      <c r="A29" t="s">
+        <v>288</v>
+      </c>
+      <c r="B29" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9">
+      <c r="A30" t="s">
+        <v>290</v>
+      </c>
+      <c r="B30" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9">
+      <c r="A31" t="s">
+        <v>292</v>
+      </c>
+      <c r="B31" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9">
+      <c r="A32" t="s">
+        <v>294</v>
+      </c>
+      <c r="B32" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9">
+      <c r="A33" t="s">
+        <v>296</v>
+      </c>
+      <c r="B33" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9">
+      <c r="A34" t="s">
+        <v>297</v>
+      </c>
+      <c r="B34" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9">
+      <c r="A35" t="s">
+        <v>298</v>
+      </c>
+      <c r="B35" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9">
+      <c r="A36" t="s">
+        <v>300</v>
+      </c>
+      <c r="B36" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9">
+      <c r="A37" t="s">
+        <v>302</v>
+      </c>
+      <c r="B37" t="s">
+        <v>303</v>
+      </c>
+      <c r="C37" t="s">
+        <v>233</v>
+      </c>
+      <c r="D37" t="s">
+        <v>304</v>
+      </c>
+      <c r="E37" t="s">
+        <v>272</v>
+      </c>
+      <c r="F37" t="s">
+        <v>305</v>
+      </c>
+      <c r="G37" t="s">
+        <v>237</v>
+      </c>
+      <c r="H37" t="s">
+        <v>306</v>
+      </c>
+      <c r="I37" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9">
+      <c r="A38" t="s">
+        <v>308</v>
+      </c>
+      <c r="B38" t="s">
+        <v>303</v>
+      </c>
+      <c r="C38" t="s">
+        <v>309</v>
+      </c>
+      <c r="D38" t="s">
+        <v>304</v>
+      </c>
+      <c r="E38" t="s">
+        <v>272</v>
+      </c>
+      <c r="F38" t="s">
+        <v>305</v>
+      </c>
+      <c r="G38" t="s">
+        <v>237</v>
+      </c>
+      <c r="H38" t="s">
+        <v>306</v>
+      </c>
+      <c r="I38" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9">
+      <c r="A39" t="s">
+        <v>310</v>
+      </c>
+      <c r="B39" t="s">
+        <v>303</v>
+      </c>
+      <c r="C39" t="s">
+        <v>311</v>
+      </c>
+      <c r="D39" t="s">
+        <v>304</v>
+      </c>
+      <c r="E39" t="s">
+        <v>272</v>
+      </c>
+      <c r="F39" t="s">
+        <v>305</v>
+      </c>
+      <c r="G39" t="s">
+        <v>237</v>
+      </c>
+      <c r="H39" t="s">
+        <v>306</v>
+      </c>
+      <c r="I39" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9">
+      <c r="A40" t="s">
+        <v>312</v>
+      </c>
+      <c r="B40" t="s">
+        <v>303</v>
+      </c>
+      <c r="C40" t="s">
+        <v>233</v>
+      </c>
+      <c r="D40" t="s">
+        <v>304</v>
+      </c>
+      <c r="E40" t="s">
+        <v>272</v>
+      </c>
+      <c r="F40" t="s">
+        <v>305</v>
+      </c>
+      <c r="G40" t="s">
+        <v>237</v>
+      </c>
+      <c r="H40" t="s">
+        <v>306</v>
+      </c>
+      <c r="I40" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9">
+      <c r="A41" t="s">
+        <v>313</v>
+      </c>
+      <c r="B41" t="s">
+        <v>303</v>
+      </c>
+      <c r="C41" t="s">
+        <v>314</v>
+      </c>
+      <c r="D41" t="s">
+        <v>304</v>
+      </c>
+      <c r="E41" t="s">
+        <v>272</v>
+      </c>
+      <c r="F41" t="s">
+        <v>305</v>
+      </c>
+      <c r="G41" t="s">
+        <v>237</v>
+      </c>
+      <c r="H41" t="s">
+        <v>306</v>
+      </c>
+      <c r="I41" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9">
+      <c r="A42" t="s">
+        <v>315</v>
+      </c>
+      <c r="B42" t="s">
+        <v>303</v>
+      </c>
+      <c r="C42" t="s">
+        <v>316</v>
+      </c>
+      <c r="D42" t="s">
+        <v>304</v>
+      </c>
+      <c r="E42" t="s">
+        <v>272</v>
+      </c>
+      <c r="F42" t="s">
+        <v>305</v>
+      </c>
+      <c r="G42" t="s">
+        <v>237</v>
+      </c>
+      <c r="H42" t="s">
+        <v>306</v>
+      </c>
+      <c r="I42" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9">
+      <c r="A43" t="s">
+        <v>317</v>
+      </c>
+      <c r="B43" t="s">
+        <v>303</v>
+      </c>
+      <c r="C43" t="s">
+        <v>242</v>
+      </c>
+      <c r="D43" t="s">
+        <v>304</v>
+      </c>
+      <c r="E43" t="s">
+        <v>272</v>
+      </c>
+      <c r="F43" t="s">
+        <v>305</v>
+      </c>
+      <c r="G43" t="s">
+        <v>237</v>
+      </c>
+      <c r="H43" t="s">
+        <v>306</v>
+      </c>
+      <c r="I43" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9">
+      <c r="A44" t="s">
+        <v>90</v>
+      </c>
+      <c r="B44" t="s">
+        <v>303</v>
+      </c>
+      <c r="C44" t="s">
+        <v>233</v>
+      </c>
+      <c r="D44" t="s">
+        <v>304</v>
+      </c>
+      <c r="E44" t="s">
+        <v>272</v>
+      </c>
+      <c r="F44" t="s">
+        <v>305</v>
+      </c>
+      <c r="G44" t="s">
+        <v>237</v>
+      </c>
+      <c r="H44" t="s">
+        <v>306</v>
+      </c>
+      <c r="I44" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9">
+      <c r="A45" t="s">
+        <v>318</v>
+      </c>
+      <c r="B45" t="s">
+        <v>303</v>
+      </c>
+      <c r="C45" t="s">
+        <v>233</v>
+      </c>
+      <c r="D45" t="s">
+        <v>304</v>
+      </c>
+      <c r="E45" t="s">
+        <v>272</v>
+      </c>
+      <c r="F45" t="s">
+        <v>305</v>
+      </c>
+      <c r="G45" t="s">
+        <v>237</v>
+      </c>
+      <c r="H45" t="s">
+        <v>306</v>
+      </c>
+      <c r="I45" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9">
+      <c r="A46" t="s">
+        <v>319</v>
+      </c>
+      <c r="B46" t="s">
+        <v>303</v>
+      </c>
+      <c r="C46" t="s">
+        <v>320</v>
+      </c>
+      <c r="D46" t="s">
+        <v>321</v>
+      </c>
+      <c r="E46" t="s">
+        <v>322</v>
+      </c>
+      <c r="F46" t="s">
+        <v>253</v>
+      </c>
+      <c r="G46" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9">
+      <c r="A47" t="s">
+        <v>323</v>
+      </c>
+      <c r="B47" t="s">
+        <v>303</v>
+      </c>
+      <c r="C47" t="s">
+        <v>291</v>
+      </c>
+      <c r="D47" t="s">
+        <v>321</v>
+      </c>
+      <c r="E47" t="s">
+        <v>242</v>
+      </c>
+      <c r="F47" t="s">
+        <v>253</v>
+      </c>
+      <c r="G47" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9">
+      <c r="A48" t="s">
+        <v>324</v>
+      </c>
+      <c r="B48" t="s">
+        <v>303</v>
+      </c>
+      <c r="C48" t="s">
+        <v>291</v>
+      </c>
+      <c r="D48" t="s">
+        <v>321</v>
+      </c>
+      <c r="E48" t="s">
+        <v>242</v>
+      </c>
+      <c r="F48" t="s">
+        <v>253</v>
+      </c>
+      <c r="G48" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7">
+      <c r="A49" t="s">
+        <v>325</v>
+      </c>
+      <c r="B49" t="s">
+        <v>303</v>
+      </c>
+      <c r="C49" t="s">
+        <v>320</v>
+      </c>
+      <c r="D49" t="s">
+        <v>321</v>
+      </c>
+      <c r="E49" t="s">
+        <v>242</v>
+      </c>
+      <c r="F49" t="s">
+        <v>253</v>
+      </c>
+      <c r="G49" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7">
+      <c r="A50" t="s">
+        <v>326</v>
+      </c>
+      <c r="B50" t="s">
+        <v>303</v>
+      </c>
+      <c r="C50" t="s">
+        <v>327</v>
+      </c>
+      <c r="D50" t="s">
+        <v>253</v>
+      </c>
+      <c r="E50" t="s">
+        <v>254</v>
       </c>
     </row>
   </sheetData>
